--- a/references/stage_03/excel/M-curvatura.xlsx
+++ b/references/stage_03/excel/M-curvatura.xlsx
@@ -5,19 +5,26 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab_PBD_RC\references\stage_02\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab_PBD_RC\references\stage_03\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478B2E4A-FA5E-4406-9EA7-2385822B10CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE0A2A0-4AE8-43E9-827F-544EB5447330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{FE6579DD-745D-47C9-9E78-1D77FF680E80}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="712" firstSheet="2" activeTab="9" xr2:uid="{FE6579DD-745D-47C9-9E78-1D77FF680E80}"/>
   </bookViews>
   <sheets>
-    <sheet name="VIGA T- P2" sheetId="1" r:id="rId1"/>
-    <sheet name="VIGA T- P6" sheetId="2" r:id="rId2"/>
-    <sheet name="VIGA T- P8" sheetId="3" r:id="rId3"/>
+    <sheet name="V1 (2-3)T" sheetId="1" r:id="rId1"/>
+    <sheet name="V1 (1-2 y 3-4)T" sheetId="2" r:id="rId2"/>
+    <sheet name="V2 (2-3, C-D y A-B)L" sheetId="3" r:id="rId3"/>
+    <sheet name="V2 (1-2 y 3-4)L " sheetId="4" r:id="rId4"/>
+    <sheet name="V2 (C-B)L " sheetId="5" r:id="rId5"/>
+    <sheet name="V2 (D-C y B-A)T" sheetId="6" r:id="rId6"/>
+    <sheet name="V2 (C-B)T" sheetId="7" r:id="rId7"/>
+    <sheet name="V3 (D-C Y B-A)T" sheetId="8" r:id="rId8"/>
+    <sheet name="V3 (C-B)T" sheetId="10" r:id="rId9"/>
+    <sheet name="V2(0-1 Y 4-5)35X50" sheetId="9" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,13 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
-  <si>
-    <t>VIGA T-P2</t>
-  </si>
-  <si>
-    <t>VIGA T - INV- P2</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="21">
   <si>
     <t xml:space="preserve">   Curvature (rad/m)</t>
   </si>
@@ -58,16 +59,58 @@
     <t xml:space="preserve">   Curvature (mrad/m)</t>
   </si>
   <si>
-    <t>VIGA T-P6</t>
+    <t>V1 (2-3)T</t>
   </si>
   <si>
-    <t>VIGA T - INV- P6</t>
+    <t>V1 (2-3)T-INV</t>
   </si>
   <si>
-    <t>VIGA T-P8</t>
+    <t>V1 (1-2 y 3-4)T</t>
   </si>
   <si>
-    <t>VIGA T - INV- P8</t>
+    <t>V1 (1-2 y 3-4)T-INV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 (C-B)L </t>
+  </si>
+  <si>
+    <t>V2 (C-B)L -INV</t>
+  </si>
+  <si>
+    <t>V2 (D-C y B-A)T</t>
+  </si>
+  <si>
+    <t>V2 (D-C y B-A)T-INV</t>
+  </si>
+  <si>
+    <t>V2 (C-B)LT</t>
+  </si>
+  <si>
+    <t>V2 (C-B)T -INV</t>
+  </si>
+  <si>
+    <t>V3 (C-B)T</t>
+  </si>
+  <si>
+    <t>V3 (C-B)T -INV</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>V2-INV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 (1-2 y 3-4)L </t>
+  </si>
+  <si>
+    <t>V2 (1-2 y 3-4)L -INV</t>
+  </si>
+  <si>
+    <t>V2 (2-3, C-D y A-B)L</t>
+  </si>
+  <si>
+    <t>V2 (2-3, C-D y A-B)L-INV</t>
   </si>
 </sst>
 </file>
@@ -91,7 +134,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -99,12 +142,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,29 +498,903 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA5C53BE-DD51-4DE1-B877-80169304E385}">
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>6.7000000000000002E-5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>22.745000000000001</v>
+      </c>
+      <c r="C5" s="1">
+        <v>-6.7000000000000002E-5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-22.725999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>1.47E-4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>50.037999999999997</v>
+      </c>
+      <c r="C6" s="1">
+        <v>-4.6700000000000002E-4</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-159.078</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>2.1100000000000001E-4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>71.873000000000005</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-5.4700000000000007E-4</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-186.346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>2.6200000000000003E-4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>89.340999999999994</v>
+      </c>
+      <c r="C8" s="1">
+        <v>-5.5900000000000004E-4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-190.709</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>3.0299999999999999E-4</v>
+      </c>
+      <c r="B9" s="1">
+        <v>103.315</v>
+      </c>
+      <c r="C9" s="1">
+        <v>-5.6999999999999998E-4</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-194.19900000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>3.0899999999999998E-4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>105.551</v>
+      </c>
+      <c r="C10" s="1">
+        <v>-5.7799999999999995E-4</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-169.876</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>3.1500000000000001E-4</v>
+      </c>
+      <c r="B11" s="1">
+        <v>102.27800000000001</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-6.11E-4</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-173.554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>3.3600000000000004E-4</v>
+      </c>
+      <c r="B12" s="1">
+        <v>98.474000000000004</v>
+      </c>
+      <c r="C12" s="1">
+        <v>-8.6700000000000004E-4</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-200.75800000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>4.6700000000000002E-4</v>
+      </c>
+      <c r="B13" s="1">
+        <v>114.46</v>
+      </c>
+      <c r="C13" s="1">
+        <v>-1.2669999999999999E-3</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-237.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>8.6700000000000004E-4</v>
+      </c>
+      <c r="B14" s="1">
+        <v>148.77099999999999</v>
+      </c>
+      <c r="C14" s="1">
+        <v>-1.6670000000000001E-3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>-273.09800000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>1.2669999999999999E-3</v>
+      </c>
+      <c r="B15" s="1">
+        <v>179.691</v>
+      </c>
+      <c r="C15" s="1">
+        <v>-2.0670000000000003E-3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>-308.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>1.6670000000000001E-3</v>
+      </c>
+      <c r="B16" s="1">
+        <v>210.40299999999999</v>
+      </c>
+      <c r="C16" s="1">
+        <v>-2.467E-3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>-343.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>2.0670000000000003E-3</v>
+      </c>
+      <c r="B17" s="1">
+        <v>241.27099999999999</v>
+      </c>
+      <c r="C17" s="1">
+        <v>-2.8670000000000002E-3</v>
+      </c>
+      <c r="D17" s="1">
+        <v>-378.404</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>2.467E-3</v>
+      </c>
+      <c r="B18" s="1">
+        <v>272.363</v>
+      </c>
+      <c r="C18" s="1">
+        <v>-3.2669999999999999E-3</v>
+      </c>
+      <c r="D18" s="1">
+        <v>-413.83100000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>2.8670000000000002E-3</v>
+      </c>
+      <c r="B19" s="1">
+        <v>303.66000000000003</v>
+      </c>
+      <c r="C19" s="1">
+        <v>-3.6669999999999997E-3</v>
+      </c>
+      <c r="D19" s="1">
+        <v>-449.423</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>3.2669999999999999E-3</v>
+      </c>
+      <c r="B20" s="1">
+        <v>335.12599999999998</v>
+      </c>
+      <c r="C20" s="1">
+        <v>-4.0670000000000003E-3</v>
+      </c>
+      <c r="D20" s="1">
+        <v>-485.14800000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>3.6669999999999997E-3</v>
+      </c>
+      <c r="B21" s="1">
+        <v>366.73399999999998</v>
+      </c>
+      <c r="C21" s="1">
+        <v>-4.4729999999999995E-3</v>
+      </c>
+      <c r="D21" s="1">
+        <v>-521.55899999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>4.0670000000000003E-3</v>
+      </c>
+      <c r="B22" s="1">
+        <v>398.46300000000002</v>
+      </c>
+      <c r="C22" s="1">
+        <v>-4.921E-3</v>
+      </c>
+      <c r="D22" s="1">
+        <v>-561.67700000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>4.4729999999999995E-3</v>
+      </c>
+      <c r="B23" s="1">
+        <v>430.82299999999998</v>
+      </c>
+      <c r="C23" s="1">
+        <v>-5.4130000000000003E-3</v>
+      </c>
+      <c r="D23" s="1">
+        <v>-605.84400000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>4.921E-3</v>
+      </c>
+      <c r="B24" s="1">
+        <v>466.52100000000002</v>
+      </c>
+      <c r="C24" s="1">
+        <v>-5.9540000000000001E-3</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-654.40899999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>5.4130000000000003E-3</v>
+      </c>
+      <c r="B25" s="1">
+        <v>505.89100000000002</v>
+      </c>
+      <c r="C25" s="1">
+        <v>-6.5490000000000001E-3</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-707.726</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>5.9540000000000001E-3</v>
+      </c>
+      <c r="B26" s="1">
+        <v>549.28300000000002</v>
+      </c>
+      <c r="C26" s="1">
+        <v>-7.2039999999999995E-3</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-766.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
+        <v>6.5490000000000001E-3</v>
+      </c>
+      <c r="B27" s="1">
+        <v>574.48299999999995</v>
+      </c>
+      <c r="C27" s="1">
+        <v>-7.9249999999999998E-3</v>
+      </c>
+      <c r="D27" s="1">
+        <v>-808.149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>7.2039999999999995E-3</v>
+      </c>
+      <c r="B28" s="1">
+        <v>583.05100000000004</v>
+      </c>
+      <c r="C28" s="1">
+        <v>-8.7170000000000008E-3</v>
+      </c>
+      <c r="D28" s="1">
+        <v>-812.822</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>7.9249999999999998E-3</v>
+      </c>
+      <c r="B29" s="1">
+        <v>591.52700000000004</v>
+      </c>
+      <c r="C29" s="1">
+        <v>-9.5890000000000003E-3</v>
+      </c>
+      <c r="D29" s="1">
+        <v>-819.524</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>8.7170000000000008E-3</v>
+      </c>
+      <c r="B30" s="1">
+        <v>598.54</v>
+      </c>
+      <c r="C30" s="1">
+        <v>-1.0548E-2</v>
+      </c>
+      <c r="D30" s="1">
+        <v>-826.03599999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>9.5890000000000003E-3</v>
+      </c>
+      <c r="B31" s="1">
+        <v>605.68799999999999</v>
+      </c>
+      <c r="C31" s="1">
+        <v>-1.1603E-2</v>
+      </c>
+      <c r="D31" s="1">
+        <v>-832.625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>1.0548E-2</v>
+      </c>
+      <c r="B32" s="1">
+        <v>612.99800000000005</v>
+      </c>
+      <c r="C32" s="1">
+        <v>-1.2763E-2</v>
+      </c>
+      <c r="D32" s="1">
+        <v>-839.30499999999995</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
+        <v>1.1603E-2</v>
+      </c>
+      <c r="B33" s="1">
+        <v>620.50199999999995</v>
+      </c>
+      <c r="C33" s="1">
+        <v>-1.4038999999999999E-2</v>
+      </c>
+      <c r="D33" s="1">
+        <v>-846.08399999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
+        <v>1.2763E-2</v>
+      </c>
+      <c r="B34" s="1">
+        <v>628.16</v>
+      </c>
+      <c r="C34" s="1">
+        <v>-1.5443E-2</v>
+      </c>
+      <c r="D34" s="1">
+        <v>-852.94100000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
+        <v>1.4038999999999999E-2</v>
+      </c>
+      <c r="B35" s="1">
+        <v>633.95100000000002</v>
+      </c>
+      <c r="C35" s="1">
+        <v>-1.6986999999999999E-2</v>
+      </c>
+      <c r="D35" s="1">
+        <v>-859.75800000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
+        <v>1.5443E-2</v>
+      </c>
+      <c r="B36" s="1">
+        <v>637.08900000000006</v>
+      </c>
+      <c r="C36" s="1">
+        <v>-1.7327000000000002E-2</v>
+      </c>
+      <c r="D36" s="1">
+        <v>-861.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
+        <v>1.6986999999999999E-2</v>
+      </c>
+      <c r="B37" s="1">
+        <v>640.20399999999995</v>
+      </c>
+      <c r="C37" s="1">
+        <v>-1.7599E-2</v>
+      </c>
+      <c r="D37" s="1">
+        <v>-862.56600000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
+        <v>1.8686000000000001E-2</v>
+      </c>
+      <c r="B38" s="1">
+        <v>643.41200000000003</v>
+      </c>
+      <c r="C38" s="1">
+        <v>-1.7815999999999999E-2</v>
+      </c>
+      <c r="D38" s="1">
+        <v>-863.48900000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
+        <v>2.0555E-2</v>
+      </c>
+      <c r="B39" s="1">
+        <v>646.96699999999998</v>
+      </c>
+      <c r="C39" s="1">
+        <v>-1.7989999999999999E-2</v>
+      </c>
+      <c r="D39" s="1">
+        <v>-864.00900000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
+        <v>2.2609999999999998E-2</v>
+      </c>
+      <c r="B40" s="1">
+        <v>650.70399999999995</v>
+      </c>
+      <c r="C40" s="1">
+        <v>-1.813E-2</v>
+      </c>
+      <c r="D40" s="1">
+        <v>-864.65599999999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
+        <v>2.4870999999999997E-2</v>
+      </c>
+      <c r="B41" s="1">
+        <v>654.45500000000004</v>
+      </c>
+      <c r="C41" s="1">
+        <v>-1.8241E-2</v>
+      </c>
+      <c r="D41" s="1">
+        <v>-865.19600000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
+        <v>2.7358E-2</v>
+      </c>
+      <c r="B42" s="1">
+        <v>658.40099999999995</v>
+      </c>
+      <c r="C42" s="1">
+        <v>-1.8329999999999999E-2</v>
+      </c>
+      <c r="D42" s="1">
+        <v>-865.64200000000005</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
+        <v>3.0094000000000003E-2</v>
+      </c>
+      <c r="B43" s="1">
+        <v>662.88300000000004</v>
+      </c>
+      <c r="C43" s="1">
+        <v>-1.8401000000000001E-2</v>
+      </c>
+      <c r="D43" s="1">
+        <v>-865.90700000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
+        <v>3.3104000000000001E-2</v>
+      </c>
+      <c r="B44" s="1">
+        <v>667.60599999999999</v>
+      </c>
+      <c r="C44" s="1">
+        <v>-1.8686000000000001E-2</v>
+      </c>
+      <c r="D44" s="1">
+        <v>-867.01300000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
+        <v>3.6414000000000002E-2</v>
+      </c>
+      <c r="B45" s="1">
+        <v>675.75199999999995</v>
+      </c>
+      <c r="C45" s="1">
+        <v>-2.0555E-2</v>
+      </c>
+      <c r="D45" s="1">
+        <v>-874.08799999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
+        <v>4.0055999999999994E-2</v>
+      </c>
+      <c r="B46" s="1">
+        <v>687.21100000000001</v>
+      </c>
+      <c r="C46" s="1">
+        <v>-2.2609999999999998E-2</v>
+      </c>
+      <c r="D46" s="1">
+        <v>-880.78599999999994</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
+        <v>4.4061000000000003E-2</v>
+      </c>
+      <c r="B47" s="1">
+        <v>700.86099999999999</v>
+      </c>
+      <c r="C47" s="1">
+        <v>-2.4870999999999997E-2</v>
+      </c>
+      <c r="D47" s="1">
+        <v>-886.86800000000005</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
+        <v>4.4942000000000003E-2</v>
+      </c>
+      <c r="B48" s="1">
+        <v>703.78599999999994</v>
+      </c>
+      <c r="C48" s="1">
+        <v>-2.7358E-2</v>
+      </c>
+      <c r="D48" s="1">
+        <v>-892.21400000000006</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
+        <v>4.5647E-2</v>
+      </c>
+      <c r="B49" s="1">
+        <v>706.1</v>
+      </c>
+      <c r="C49" s="1">
+        <v>-3.0094000000000003E-2</v>
+      </c>
+      <c r="D49" s="1">
+        <v>-896.48199999999997</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
+        <v>4.6210999999999995E-2</v>
+      </c>
+      <c r="B50" s="1">
+        <v>708.04200000000003</v>
+      </c>
+      <c r="C50" s="1">
+        <v>-3.3104000000000001E-2</v>
+      </c>
+      <c r="D50" s="1">
+        <v>-899.41499999999996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
+        <v>4.6302000000000003E-2</v>
+      </c>
+      <c r="B51" s="1">
+        <v>708.25300000000004</v>
+      </c>
+      <c r="C51" s="1">
+        <v>-3.6414000000000002E-2</v>
+      </c>
+      <c r="D51" s="1">
+        <v>-897.43899999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
+        <v>4.6374000000000005E-2</v>
+      </c>
+      <c r="B52" s="1">
+        <v>708.47299999999996</v>
+      </c>
+      <c r="C52" s="1">
+        <v>-4.0055999999999994E-2</v>
+      </c>
+      <c r="D52" s="1">
+        <v>-890.59299999999996</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
+        <v>4.6431E-2</v>
+      </c>
+      <c r="B53" s="1">
+        <v>708.66600000000005</v>
+      </c>
+      <c r="C53" s="1">
+        <v>-4.4061000000000003E-2</v>
+      </c>
+      <c r="D53" s="1">
+        <v>-887.822</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
+        <v>4.6662999999999996E-2</v>
+      </c>
+      <c r="B54" s="1">
+        <v>709.43200000000002</v>
+      </c>
+      <c r="C54" s="1">
+        <v>-4.8466999999999996E-2</v>
+      </c>
+      <c r="D54" s="1">
+        <v>-877.42399999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="1">
+        <v>4.8466999999999996E-2</v>
+      </c>
+      <c r="B55" s="1">
+        <v>713.24699999999996</v>
+      </c>
+      <c r="C55" s="1">
+        <v>-5.3314E-2</v>
+      </c>
+      <c r="D55" s="1">
+        <v>-868.48400000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="1">
+        <v>5.3314E-2</v>
+      </c>
+      <c r="B56" s="1">
+        <v>722.66600000000005</v>
+      </c>
+      <c r="C56" s="1">
+        <v>-5.8645000000000003E-2</v>
+      </c>
+      <c r="D56" s="1">
+        <v>-861.86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="1">
+        <v>5.8645000000000003E-2</v>
+      </c>
+      <c r="B57" s="1">
+        <v>731.84100000000001</v>
+      </c>
+      <c r="C57" s="1">
+        <v>-6.4510000000000012E-2</v>
+      </c>
+      <c r="D57" s="1">
+        <v>-858.976</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="1">
+        <v>6.4510000000000012E-2</v>
+      </c>
+      <c r="B58" s="1">
+        <v>740.26</v>
+      </c>
+      <c r="C58" s="1">
+        <v>-7.0960999999999996E-2</v>
+      </c>
+      <c r="D58" s="1">
+        <v>-829.11099999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="1">
+        <v>7.0960999999999996E-2</v>
+      </c>
+      <c r="B59" s="1">
+        <v>747.26599999999996</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="1">
+        <v>7.8057000000000001E-2</v>
+      </c>
+      <c r="B60" s="1">
+        <v>751.94100000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="1">
+        <v>8.5862999999999995E-2</v>
+      </c>
+      <c r="B61" s="1">
+        <v>753.75400000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="1">
+        <v>9.4448999999999991E-2</v>
+      </c>
+      <c r="B62" s="1">
+        <v>752.80799999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="1">
+        <v>0.103894</v>
+      </c>
+      <c r="B63" s="1">
+        <v>750.13900000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="1">
+        <v>0.114283</v>
+      </c>
+      <c r="B64" s="1">
+        <v>747.93600000000004</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="1">
+        <v>0.12571199999999999</v>
+      </c>
+      <c r="B65" s="1">
+        <v>746.54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="1">
+        <v>0.13828299999999999</v>
+      </c>
+      <c r="B66" s="1">
+        <v>748.09299999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2391D36C-E0C5-41C0-9D64-BD1EB5FEB729}">
+  <dimension ref="A1:D65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -480,908 +1413,856 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>5.1E-5</v>
+        <v>6.7000000000000002E-5</v>
       </c>
       <c r="B5">
-        <v>22.766999999999999</v>
+        <v>8.6470000000000002</v>
       </c>
       <c r="C5">
-        <v>-5.1E-5</v>
+        <v>-6.7000000000000002E-5</v>
       </c>
       <c r="D5">
-        <v>-22.762</v>
+        <v>-8.6470000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>1.1300000000000001E-4</v>
+        <v>1.47E-4</v>
       </c>
       <c r="B6">
-        <v>50.085999999999999</v>
+        <v>19.024000000000001</v>
       </c>
       <c r="C6">
-        <v>-3.59E-4</v>
+        <v>-1.47E-4</v>
       </c>
       <c r="D6">
-        <v>-159.28800000000001</v>
+        <v>-19.024000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>1.6200000000000001E-4</v>
+        <v>2.1100000000000001E-4</v>
       </c>
       <c r="B7">
-        <v>71.941000000000003</v>
+        <v>27.324999999999999</v>
       </c>
       <c r="C7">
-        <v>-3.7100000000000002E-4</v>
+        <v>-2.1100000000000001E-4</v>
       </c>
       <c r="D7">
-        <v>-164.745</v>
+        <v>-27.324999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>2.0100000000000001E-4</v>
+        <v>2.6200000000000003E-4</v>
       </c>
       <c r="B8">
-        <v>89.424999999999997</v>
+        <v>33.966000000000001</v>
       </c>
       <c r="C8">
-        <v>-3.8099999999999999E-4</v>
+        <v>-2.6200000000000003E-4</v>
       </c>
       <c r="D8">
-        <v>-169.11099999999999</v>
+        <v>-33.966000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>2.3300000000000003E-4</v>
+        <v>3.0299999999999999E-4</v>
       </c>
       <c r="B9">
-        <v>103.411</v>
+        <v>39.279000000000003</v>
       </c>
       <c r="C9">
-        <v>-3.8900000000000002E-4</v>
+        <v>-3.0299999999999999E-4</v>
       </c>
       <c r="D9">
-        <v>-172.60300000000001</v>
+        <v>-39.279000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>2.5799999999999998E-4</v>
+        <v>3.3600000000000004E-4</v>
       </c>
       <c r="B10">
-        <v>114.599</v>
+        <v>43.529000000000003</v>
       </c>
       <c r="C10">
-        <v>-3.9500000000000001E-4</v>
+        <v>-3.3600000000000004E-4</v>
       </c>
       <c r="D10">
-        <v>-175.39599999999999</v>
+        <v>-43.529000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>2.7800000000000004E-4</v>
+        <v>3.6199999999999996E-4</v>
       </c>
       <c r="B11">
-        <v>123.54900000000001</v>
+        <v>46.929000000000002</v>
       </c>
       <c r="C11">
-        <v>-4.0000000000000002E-4</v>
+        <v>-3.6199999999999996E-4</v>
       </c>
       <c r="D11">
-        <v>-177.631</v>
+        <v>-46.929000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>2.8199999999999997E-4</v>
+        <v>3.8299999999999999E-4</v>
       </c>
       <c r="B12">
-        <v>124.98099999999999</v>
+        <v>49.649000000000001</v>
       </c>
       <c r="C12">
-        <v>-4.0400000000000001E-4</v>
+        <v>-3.8299999999999999E-4</v>
       </c>
       <c r="D12">
-        <v>-179.41900000000001</v>
+        <v>-49.649000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>2.8399999999999996E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="B13">
-        <v>126.127</v>
+        <v>51.826000000000001</v>
       </c>
       <c r="C13">
-        <v>-4.08E-4</v>
+        <v>-4.0000000000000002E-4</v>
       </c>
       <c r="D13">
-        <v>-180.84899999999999</v>
+        <v>-51.826000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>2.8599999999999996E-4</v>
+        <v>4.0200000000000001E-4</v>
       </c>
       <c r="B14">
-        <v>127.04300000000001</v>
+        <v>52.173999999999999</v>
       </c>
       <c r="C14">
-        <v>-4.0999999999999999E-4</v>
+        <v>-4.0200000000000001E-4</v>
       </c>
       <c r="D14">
-        <v>-181.99299999999999</v>
+        <v>-52.173999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>2.8799999999999995E-4</v>
+        <v>4.0400000000000001E-4</v>
       </c>
       <c r="B15">
-        <v>115.932</v>
+        <v>52.176000000000002</v>
       </c>
       <c r="C15">
-        <v>-4.1199999999999999E-4</v>
+        <v>-4.0400000000000001E-4</v>
       </c>
       <c r="D15">
-        <v>-182.89599999999999</v>
+        <v>-52.176000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>2.9399999999999999E-4</v>
+        <v>4.1299999999999996E-4</v>
       </c>
       <c r="B16">
-        <v>110.395</v>
+        <v>51.128</v>
       </c>
       <c r="C16">
-        <v>-4.2099999999999999E-4</v>
+        <v>-4.1299999999999996E-4</v>
       </c>
       <c r="D16">
-        <v>-144.90100000000001</v>
+        <v>-51.128</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>3.59E-4</v>
+        <v>4.6700000000000002E-4</v>
       </c>
       <c r="B17">
-        <v>118.102</v>
+        <v>52.301000000000002</v>
       </c>
       <c r="C17">
-        <v>-6.6700000000000006E-4</v>
+        <v>-4.6700000000000002E-4</v>
       </c>
       <c r="D17">
-        <v>-168.87100000000001</v>
+        <v>-52.301000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>6.6700000000000006E-4</v>
+        <v>8.6700000000000004E-4</v>
       </c>
       <c r="B18">
-        <v>143.06</v>
+        <v>74.924000000000007</v>
       </c>
       <c r="C18">
-        <v>-9.7399999999999993E-4</v>
+        <v>-8.6700000000000004E-4</v>
       </c>
       <c r="D18">
-        <v>-190.14500000000001</v>
+        <v>-74.924000000000007</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>9.7399999999999993E-4</v>
+        <v>1.2669999999999999E-3</v>
       </c>
       <c r="B19">
-        <v>162.37</v>
+        <v>94.626999999999995</v>
       </c>
       <c r="C19">
-        <v>-1.2819999999999999E-3</v>
+        <v>-1.2669999999999999E-3</v>
       </c>
       <c r="D19">
-        <v>-209.345</v>
+        <v>-94.626999999999995</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>1.2819999999999999E-3</v>
+        <v>1.6670000000000001E-3</v>
       </c>
       <c r="B20">
-        <v>181.15199999999999</v>
+        <v>113.92</v>
       </c>
       <c r="C20">
-        <v>-1.5900000000000001E-3</v>
+        <v>-1.6670000000000001E-3</v>
       </c>
       <c r="D20">
-        <v>-228.24199999999999</v>
+        <v>-113.92</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>1.5900000000000001E-3</v>
+        <v>2.0670000000000003E-3</v>
       </c>
       <c r="B21">
-        <v>200.12200000000001</v>
+        <v>133.16499999999999</v>
       </c>
       <c r="C21">
-        <v>-1.897E-3</v>
+        <v>-2.0670000000000003E-3</v>
       </c>
       <c r="D21">
-        <v>-247.14400000000001</v>
+        <v>-133.16499999999999</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>1.897E-3</v>
+        <v>2.467E-3</v>
       </c>
       <c r="B22">
-        <v>219.37200000000001</v>
+        <v>152.43600000000001</v>
       </c>
       <c r="C22">
-        <v>-2.2049999999999999E-3</v>
+        <v>-2.467E-3</v>
       </c>
       <c r="D22">
-        <v>-266.30799999999999</v>
+        <v>-152.43600000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>2.2049999999999999E-3</v>
+        <v>2.8670000000000002E-3</v>
       </c>
       <c r="B23">
-        <v>238.93600000000001</v>
+        <v>171.76300000000001</v>
       </c>
       <c r="C23">
-        <v>-2.513E-3</v>
+        <v>-2.8670000000000002E-3</v>
       </c>
       <c r="D23">
-        <v>-285.71800000000002</v>
+        <v>-171.76300000000001</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>2.513E-3</v>
+        <v>3.2669999999999999E-3</v>
       </c>
       <c r="B24">
-        <v>258.78199999999998</v>
+        <v>191.14</v>
       </c>
       <c r="C24">
-        <v>-2.8210000000000002E-3</v>
+        <v>-3.2669999999999999E-3</v>
       </c>
       <c r="D24">
-        <v>-305.33499999999998</v>
+        <v>-191.14</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>2.8210000000000002E-3</v>
+        <v>3.6669999999999997E-3</v>
       </c>
       <c r="B25">
-        <v>278.846</v>
+        <v>210.55699999999999</v>
       </c>
       <c r="C25">
-        <v>-3.1280000000000001E-3</v>
+        <v>-3.6669999999999997E-3</v>
       </c>
       <c r="D25">
-        <v>-325.14600000000002</v>
+        <v>-210.55699999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>3.1280000000000001E-3</v>
+        <v>4.0670000000000003E-3</v>
       </c>
       <c r="B26">
-        <v>299.09800000000001</v>
+        <v>230.00700000000001</v>
       </c>
       <c r="C26">
-        <v>-3.441E-3</v>
+        <v>-4.0670000000000003E-3</v>
       </c>
       <c r="D26">
-        <v>-345.42899999999997</v>
+        <v>-230.00700000000001</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>3.441E-3</v>
+        <v>4.4729999999999995E-3</v>
       </c>
       <c r="B27">
-        <v>319.85599999999999</v>
+        <v>249.80500000000001</v>
       </c>
       <c r="C27">
-        <v>-3.7850000000000002E-3</v>
+        <v>-4.4729999999999995E-3</v>
       </c>
       <c r="D27">
-        <v>-367.88900000000001</v>
+        <v>-249.80500000000001</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>3.7850000000000002E-3</v>
+        <v>4.921E-3</v>
       </c>
       <c r="B28">
-        <v>342.53300000000002</v>
+        <v>271.596</v>
       </c>
       <c r="C28">
-        <v>-4.1639999999999993E-3</v>
+        <v>-4.921E-3</v>
       </c>
       <c r="D28">
-        <v>-392.298</v>
+        <v>-271.596</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>4.1639999999999993E-3</v>
+        <v>5.4130000000000003E-3</v>
       </c>
       <c r="B29">
-        <v>363.25599999999997</v>
+        <v>295.57100000000003</v>
       </c>
       <c r="C29">
-        <v>-4.5799999999999999E-3</v>
+        <v>-5.4130000000000003E-3</v>
       </c>
       <c r="D29">
-        <v>-402.67</v>
+        <v>-295.57100000000003</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>4.5799999999999999E-3</v>
+        <v>5.9540000000000001E-3</v>
       </c>
       <c r="B30">
-        <v>364.81099999999998</v>
+        <v>321.928</v>
       </c>
       <c r="C30">
-        <v>-5.0379999999999999E-3</v>
+        <v>-5.9540000000000001E-3</v>
       </c>
       <c r="D30">
-        <v>-403.97300000000001</v>
+        <v>-321.928</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>5.0379999999999999E-3</v>
+        <v>6.5490000000000001E-3</v>
       </c>
       <c r="B31">
-        <v>366.94799999999998</v>
+        <v>350.88099999999997</v>
       </c>
       <c r="C31">
-        <v>-5.5420000000000001E-3</v>
+        <v>-6.5490000000000001E-3</v>
       </c>
       <c r="D31">
-        <v>-406.017</v>
+        <v>-350.88099999999997</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>5.5420000000000001E-3</v>
+        <v>7.2039999999999995E-3</v>
       </c>
       <c r="B32">
-        <v>370.31700000000001</v>
+        <v>382.64299999999997</v>
       </c>
       <c r="C32">
-        <v>-6.0959999999999999E-3</v>
+        <v>-7.2039999999999995E-3</v>
       </c>
       <c r="D32">
-        <v>-409.654</v>
+        <v>-382.64299999999997</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>6.0959999999999999E-3</v>
+        <v>7.9249999999999998E-3</v>
       </c>
       <c r="B33">
-        <v>374.03300000000002</v>
+        <v>409.90100000000001</v>
       </c>
       <c r="C33">
-        <v>-6.7060000000000002E-3</v>
+        <v>-7.9249999999999998E-3</v>
       </c>
       <c r="D33">
-        <v>-413.51600000000002</v>
+        <v>-409.90100000000001</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>6.7060000000000002E-3</v>
+        <v>8.7170000000000008E-3</v>
       </c>
       <c r="B34">
-        <v>378.05500000000001</v>
+        <v>411.63499999999999</v>
       </c>
       <c r="C34">
-        <v>-7.3760000000000006E-3</v>
+        <v>-8.7170000000000008E-3</v>
       </c>
       <c r="D34">
-        <v>-417.61200000000002</v>
+        <v>-411.63499999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>7.3760000000000006E-3</v>
+        <v>9.5890000000000003E-3</v>
       </c>
       <c r="B35">
-        <v>382.41800000000001</v>
+        <v>414.31400000000002</v>
       </c>
       <c r="C35">
-        <v>-8.1140000000000014E-3</v>
+        <v>-9.5890000000000003E-3</v>
       </c>
       <c r="D35">
-        <v>-421.91300000000001</v>
+        <v>-414.31400000000002</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>8.1140000000000014E-3</v>
+        <v>1.0548E-2</v>
       </c>
       <c r="B36">
-        <v>387.43299999999999</v>
+        <v>417.351</v>
       </c>
       <c r="C36">
-        <v>-8.9250000000000006E-3</v>
+        <v>-1.0548E-2</v>
       </c>
       <c r="D36">
-        <v>-426.47500000000002</v>
+        <v>-417.351</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>8.9250000000000006E-3</v>
+        <v>1.1603E-2</v>
       </c>
       <c r="B37">
-        <v>393.09500000000003</v>
+        <v>420.423</v>
       </c>
       <c r="C37">
-        <v>-9.8180000000000003E-3</v>
+        <v>-1.1603E-2</v>
       </c>
       <c r="D37">
-        <v>-431.30500000000001</v>
+        <v>-420.423</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>9.8180000000000003E-3</v>
+        <v>1.2763E-2</v>
       </c>
       <c r="B38">
-        <v>399.339</v>
+        <v>423.57100000000003</v>
       </c>
       <c r="C38">
-        <v>-1.0799E-2</v>
+        <v>-1.2763E-2</v>
       </c>
       <c r="D38">
-        <v>-436.40199999999999</v>
+        <v>-423.57100000000003</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>1.0799E-2</v>
+        <v>1.4038999999999999E-2</v>
       </c>
       <c r="B39">
-        <v>406.12400000000002</v>
+        <v>426.81700000000001</v>
       </c>
       <c r="C39">
-        <v>-1.1878999999999999E-2</v>
+        <v>-1.4038999999999999E-2</v>
       </c>
       <c r="D39">
-        <v>-441.83699999999999</v>
+        <v>-426.81700000000001</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>1.1878999999999999E-2</v>
+        <v>1.5443E-2</v>
       </c>
       <c r="B40">
-        <v>410.46</v>
+        <v>430.16699999999997</v>
       </c>
       <c r="C40">
-        <v>-1.3067E-2</v>
+        <v>-1.5443E-2</v>
       </c>
       <c r="D40">
-        <v>-447.60500000000002</v>
+        <v>-430.16699999999997</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>1.3067E-2</v>
+        <v>1.6986999999999999E-2</v>
       </c>
       <c r="B41">
-        <v>411.09</v>
+        <v>433.62599999999998</v>
       </c>
       <c r="C41">
-        <v>-1.4374000000000001E-2</v>
+        <v>-1.6986999999999999E-2</v>
       </c>
       <c r="D41">
-        <v>-453.62</v>
+        <v>-433.62599999999998</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>1.4374000000000001E-2</v>
+        <v>1.8686000000000001E-2</v>
       </c>
       <c r="B42">
-        <v>411.471</v>
+        <v>437.19099999999997</v>
       </c>
       <c r="C42">
-        <v>-1.5810999999999999E-2</v>
+        <v>-1.8686000000000001E-2</v>
       </c>
       <c r="D42">
-        <v>-459.93900000000002</v>
+        <v>-437.19099999999997</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>1.5810999999999999E-2</v>
+        <v>2.0555E-2</v>
       </c>
       <c r="B43">
-        <v>411.57600000000002</v>
+        <v>440.84699999999998</v>
       </c>
       <c r="C43">
-        <v>-1.7393000000000002E-2</v>
+        <v>-2.0555E-2</v>
       </c>
       <c r="D43">
-        <v>-466.32</v>
+        <v>-440.84699999999998</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>1.7393000000000002E-2</v>
+        <v>2.0966000000000002E-2</v>
       </c>
       <c r="B44">
-        <v>411.51499999999999</v>
+        <v>441.654</v>
       </c>
       <c r="C44">
-        <v>-1.9132000000000003E-2</v>
+        <v>-2.0966000000000002E-2</v>
       </c>
       <c r="D44">
-        <v>-472.30900000000003</v>
+        <v>-441.654</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>1.9132000000000003E-2</v>
+        <v>2.1295000000000001E-2</v>
       </c>
       <c r="B45">
-        <v>411.45699999999999</v>
+        <v>442.27300000000002</v>
       </c>
       <c r="C45">
-        <v>-2.1045000000000001E-2</v>
+        <v>-2.1295000000000001E-2</v>
       </c>
       <c r="D45">
-        <v>-471.99299999999999</v>
+        <v>-442.27300000000002</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>2.1045000000000001E-2</v>
+        <v>2.1558000000000001E-2</v>
       </c>
       <c r="B46">
-        <v>411.42700000000002</v>
+        <v>442.68700000000001</v>
       </c>
       <c r="C46">
-        <v>-2.1466000000000002E-2</v>
+        <v>-2.1558000000000001E-2</v>
       </c>
       <c r="D46">
-        <v>-471.642</v>
+        <v>-442.68700000000001</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>2.3148999999999999E-2</v>
+        <v>2.1767999999999999E-2</v>
       </c>
       <c r="B47">
-        <v>411.565</v>
+        <v>443.12299999999999</v>
       </c>
       <c r="C47">
-        <v>-2.1533E-2</v>
+        <v>-2.1767999999999999E-2</v>
       </c>
       <c r="D47">
-        <v>-471.67</v>
+        <v>-443.12299999999999</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>2.5463999999999997E-2</v>
+        <v>2.1801999999999998E-2</v>
       </c>
       <c r="B48">
-        <v>411.62</v>
+        <v>443.21600000000001</v>
       </c>
       <c r="C48">
-        <v>-2.1586999999999999E-2</v>
+        <v>-2.1801999999999998E-2</v>
       </c>
       <c r="D48">
-        <v>-471.649</v>
+        <v>-443.21600000000001</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>2.8010999999999998E-2</v>
+        <v>2.1829000000000001E-2</v>
       </c>
       <c r="B49">
-        <v>415.60500000000002</v>
+        <v>443.26400000000001</v>
       </c>
       <c r="C49">
-        <v>-2.163E-2</v>
+        <v>-2.1829000000000001E-2</v>
       </c>
       <c r="D49">
-        <v>-471.61099999999999</v>
+        <v>-443.26400000000001</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>3.0812000000000003E-2</v>
+        <v>2.1937000000000002E-2</v>
       </c>
       <c r="B50">
-        <v>420.70400000000001</v>
+        <v>443.45699999999999</v>
       </c>
       <c r="C50">
-        <v>-2.1665E-2</v>
+        <v>-2.1937000000000002E-2</v>
       </c>
       <c r="D50">
-        <v>-471.59500000000003</v>
+        <v>-443.45699999999999</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>3.3893E-2</v>
+        <v>2.2609999999999998E-2</v>
       </c>
       <c r="B51">
-        <v>426.40300000000002</v>
+        <v>444.57600000000002</v>
       </c>
       <c r="C51">
-        <v>-2.1802999999999999E-2</v>
+        <v>-2.2609999999999998E-2</v>
       </c>
       <c r="D51">
-        <v>-471.55700000000002</v>
+        <v>-444.57600000000002</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>3.7283000000000004E-2</v>
+        <v>2.4870999999999997E-2</v>
       </c>
       <c r="B52">
-        <v>432.61099999999999</v>
+        <v>447.46</v>
       </c>
       <c r="C52">
-        <v>-2.3148999999999999E-2</v>
+        <v>-2.4870999999999997E-2</v>
       </c>
       <c r="D52">
-        <v>-470.6</v>
+        <v>-447.46</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>4.1011000000000006E-2</v>
+        <v>2.7358E-2</v>
       </c>
       <c r="B53">
-        <v>439.25200000000001</v>
+        <v>448.91500000000002</v>
       </c>
       <c r="C53">
-        <v>-2.5463999999999997E-2</v>
+        <v>-2.7358E-2</v>
       </c>
       <c r="D53">
-        <v>-469.03</v>
+        <v>-448.91500000000002</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>4.5111999999999999E-2</v>
+        <v>3.0094000000000003E-2</v>
       </c>
       <c r="B54">
-        <v>446.363</v>
+        <v>448.64499999999998</v>
       </c>
       <c r="C54">
-        <v>-2.8010999999999998E-2</v>
+        <v>-3.0094000000000003E-2</v>
       </c>
       <c r="D54">
-        <v>-468.11599999999999</v>
+        <v>-448.64499999999998</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>4.6014000000000006E-2</v>
+        <v>3.3104000000000001E-2</v>
       </c>
       <c r="B55">
-        <v>447.99400000000003</v>
+        <v>447.82499999999999</v>
       </c>
       <c r="C55">
-        <v>-3.0812000000000003E-2</v>
+        <v>-3.3104000000000001E-2</v>
       </c>
       <c r="D55">
-        <v>-470.47199999999998</v>
+        <v>-447.82499999999999</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>4.6736E-2</v>
+        <v>3.6414000000000002E-2</v>
       </c>
       <c r="B56">
-        <v>449.21699999999998</v>
+        <v>446.50400000000002</v>
       </c>
       <c r="C56">
-        <v>-3.3893E-2</v>
+        <v>-3.6414000000000002E-2</v>
       </c>
       <c r="D56">
-        <v>-472.92099999999999</v>
+        <v>-446.50400000000002</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>4.7313000000000001E-2</v>
+        <v>4.0055999999999994E-2</v>
       </c>
       <c r="B57">
-        <v>450.18700000000001</v>
+        <v>446.45499999999998</v>
       </c>
       <c r="C57">
-        <v>-3.7283000000000004E-2</v>
+        <v>-4.0055999999999994E-2</v>
       </c>
       <c r="D57">
-        <v>-475.31900000000002</v>
+        <v>-446.45499999999998</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>4.7405999999999997E-2</v>
+        <v>4.4061000000000003E-2</v>
       </c>
       <c r="B58">
-        <v>450.43900000000002</v>
+        <v>447.78199999999998</v>
       </c>
       <c r="C58">
-        <v>-4.1011000000000006E-2</v>
+        <v>-4.4061000000000003E-2</v>
       </c>
       <c r="D58">
-        <v>-478</v>
+        <v>-447.78199999999998</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>4.7479999999999994E-2</v>
+        <v>4.8466999999999996E-2</v>
       </c>
       <c r="B59">
-        <v>450.40899999999999</v>
+        <v>450.39699999999999</v>
       </c>
       <c r="C59">
-        <v>-4.5111999999999999E-2</v>
+        <v>-4.8466999999999996E-2</v>
       </c>
       <c r="D59">
-        <v>-480.62799999999999</v>
+        <v>-450.39699999999999</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>4.7539000000000005E-2</v>
+        <v>5.3314E-2</v>
       </c>
       <c r="B60">
-        <v>450.51100000000002</v>
+        <v>453.38799999999998</v>
       </c>
       <c r="C60">
-        <v>-4.9623E-2</v>
+        <v>-5.3314E-2</v>
       </c>
       <c r="D60">
-        <v>-483.26</v>
+        <v>-453.38799999999998</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>4.7774999999999998E-2</v>
+        <v>5.8645000000000003E-2</v>
       </c>
       <c r="B61">
-        <v>450.96300000000002</v>
+        <v>457.25099999999998</v>
       </c>
       <c r="C61">
-        <v>-5.4585000000000002E-2</v>
+        <v>-5.8645000000000003E-2</v>
       </c>
       <c r="D61">
-        <v>-486.00599999999997</v>
+        <v>-457.25099999999998</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>4.9623E-2</v>
+        <v>6.4510000000000012E-2</v>
       </c>
       <c r="B62">
-        <v>454.1</v>
+        <v>460.52600000000001</v>
       </c>
       <c r="C62">
-        <v>-6.0044E-2</v>
+        <v>-6.4510000000000012E-2</v>
       </c>
       <c r="D62">
-        <v>-488.90600000000001</v>
+        <v>-460.52600000000001</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>5.4585000000000002E-2</v>
+        <v>7.0960999999999996E-2</v>
       </c>
       <c r="B63">
-        <v>462.08800000000002</v>
+        <v>460.85700000000003</v>
       </c>
       <c r="C63">
-        <v>-6.6047999999999996E-2</v>
+        <v>-7.0960999999999996E-2</v>
       </c>
       <c r="D63">
-        <v>-492.14</v>
+        <v>-460.85700000000003</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>6.0044E-2</v>
+        <v>7.8057000000000001E-2</v>
       </c>
       <c r="B64">
-        <v>470.13499999999999</v>
+        <v>461.89499999999998</v>
       </c>
       <c r="C64">
-        <v>-7.2653000000000009E-2</v>
+        <v>-7.8057000000000001E-2</v>
       </c>
       <c r="D64">
-        <v>-495.69400000000002</v>
+        <v>-461.89499999999998</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>6.6047999999999996E-2</v>
+        <v>8.5862999999999995E-2</v>
       </c>
       <c r="B65">
-        <v>478.17899999999997</v>
+        <v>463.964</v>
       </c>
       <c r="C65">
-        <v>-7.9918000000000003E-2</v>
+        <v>-8.5862999999999995E-2</v>
       </c>
       <c r="D65">
-        <v>-499.904</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>6.7368999999999998E-2</v>
-      </c>
-      <c r="B66">
-        <v>479.86399999999998</v>
-      </c>
-      <c r="C66">
-        <v>-8.7910000000000002E-2</v>
-      </c>
-      <c r="D66">
-        <v>-504.577</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>6.8822000000000008E-2</v>
-      </c>
-      <c r="B67">
-        <v>481.50099999999998</v>
-      </c>
-      <c r="C67">
-        <v>-8.9668000000000012E-2</v>
-      </c>
-      <c r="D67">
-        <v>-505.601</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>7.0315000000000003E-2</v>
-      </c>
-      <c r="B68">
-        <v>483.11399999999998</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>7.1840999999999988E-2</v>
-      </c>
-      <c r="B69">
-        <v>484.59899999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>7.2152000000000008E-2</v>
-      </c>
-      <c r="B70">
-        <v>484.86500000000001</v>
+        <v>-463.964</v>
       </c>
     </row>
   </sheetData>
@@ -1393,6 +2274,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5898B499-2213-49E0-9799-A339D0824B02}">
   <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1404,16 +2291,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1432,878 +2319,818 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>5.1E-5</v>
+        <v>6.7000000000000002E-5</v>
       </c>
       <c r="B5">
-        <v>22.529</v>
+        <v>17.908999999999999</v>
       </c>
       <c r="C5">
-        <v>-5.1E-5</v>
+        <v>-6.7000000000000002E-5</v>
       </c>
       <c r="D5">
-        <v>-22.524000000000001</v>
+        <v>-17.908000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>1.1300000000000001E-4</v>
+        <v>1.47E-4</v>
       </c>
       <c r="B6">
-        <v>49.563000000000002</v>
+        <v>39.4</v>
       </c>
       <c r="C6">
-        <v>-3.59E-4</v>
+        <v>-4.6700000000000002E-4</v>
       </c>
       <c r="D6">
-        <v>-157.625</v>
+        <v>-125.357</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>1.6200000000000001E-4</v>
+        <v>2.1100000000000001E-4</v>
       </c>
       <c r="B7">
-        <v>71.19</v>
+        <v>56.591999999999999</v>
       </c>
       <c r="C7">
-        <v>-3.7100000000000002E-4</v>
+        <v>-4.6999999999999999E-4</v>
       </c>
       <c r="D7">
-        <v>-163.02500000000001</v>
+        <v>-118.313</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>2.0100000000000001E-4</v>
+        <v>2.6200000000000003E-4</v>
       </c>
       <c r="B8">
-        <v>88.491</v>
+        <v>70.346000000000004</v>
       </c>
       <c r="C8">
-        <v>-3.8099999999999999E-4</v>
+        <v>-4.8299999999999998E-4</v>
       </c>
       <c r="D8">
-        <v>-167.345</v>
+        <v>-113.663</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>2.3300000000000003E-4</v>
+        <v>3.0299999999999999E-4</v>
       </c>
       <c r="B9">
-        <v>102.331</v>
+        <v>81.349000000000004</v>
       </c>
       <c r="C9">
-        <v>-3.8900000000000002E-4</v>
+        <v>-5.4700000000000007E-4</v>
       </c>
       <c r="D9">
-        <v>-170.8</v>
+        <v>-120.682</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>2.5799999999999998E-4</v>
+        <v>3.3600000000000004E-4</v>
       </c>
       <c r="B10">
-        <v>113.40300000000001</v>
+        <v>90.152000000000001</v>
       </c>
       <c r="C10">
-        <v>-3.9500000000000001E-4</v>
+        <v>-8.6700000000000004E-4</v>
       </c>
       <c r="D10">
-        <v>-173.565</v>
+        <v>-153.42400000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>2.7800000000000004E-4</v>
+        <v>3.4100000000000005E-4</v>
       </c>
       <c r="B11">
-        <v>122.26</v>
+        <v>91.56</v>
       </c>
       <c r="C11">
-        <v>-4.0000000000000002E-4</v>
+        <v>-1.2669999999999999E-3</v>
       </c>
       <c r="D11">
-        <v>-175.77600000000001</v>
+        <v>-189.15100000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>2.8199999999999997E-4</v>
+        <v>3.4499999999999998E-4</v>
       </c>
       <c r="B12">
-        <v>123.67700000000001</v>
+        <v>92.686999999999998</v>
       </c>
       <c r="C12">
-        <v>-4.0400000000000001E-4</v>
+        <v>-1.6670000000000001E-3</v>
       </c>
       <c r="D12">
-        <v>-177.54499999999999</v>
+        <v>-223.732</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>2.8399999999999996E-4</v>
+        <v>3.48E-4</v>
       </c>
       <c r="B13">
-        <v>124.81100000000001</v>
+        <v>93.587999999999994</v>
       </c>
       <c r="C13">
-        <v>-4.08E-4</v>
+        <v>-2.0670000000000003E-3</v>
       </c>
       <c r="D13">
-        <v>-178.96</v>
+        <v>-258.15600000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>2.8599999999999996E-4</v>
+        <v>3.5099999999999997E-4</v>
       </c>
       <c r="B14">
-        <v>112.22499999999999</v>
+        <v>94.31</v>
       </c>
       <c r="C14">
-        <v>-4.0999999999999999E-4</v>
+        <v>-2.467E-3</v>
       </c>
       <c r="D14">
-        <v>-180.09299999999999</v>
+        <v>-292.62599999999998</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>2.9399999999999999E-4</v>
+        <v>3.5299999999999996E-4</v>
       </c>
       <c r="B15">
-        <v>106.899</v>
+        <v>94.885999999999996</v>
       </c>
       <c r="C15">
-        <v>-4.1199999999999999E-4</v>
+        <v>-2.8670000000000002E-3</v>
       </c>
       <c r="D15">
-        <v>-180.99799999999999</v>
+        <v>-327.197</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>3.59E-4</v>
+        <v>3.5499999999999996E-4</v>
       </c>
       <c r="B16">
-        <v>115.014</v>
+        <v>95.272999999999996</v>
       </c>
       <c r="C16">
-        <v>-4.2099999999999999E-4</v>
+        <v>-3.2669999999999999E-3</v>
       </c>
       <c r="D16">
-        <v>-142.32900000000001</v>
+        <v>-361.87099999999998</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>6.6700000000000006E-4</v>
+        <v>3.6199999999999996E-4</v>
       </c>
       <c r="B17">
-        <v>137.68100000000001</v>
+        <v>91.557000000000002</v>
       </c>
       <c r="C17">
-        <v>-6.6700000000000006E-4</v>
+        <v>-3.6669999999999997E-3</v>
       </c>
       <c r="D17">
-        <v>-164.489</v>
+        <v>-396.62200000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>9.7399999999999993E-4</v>
+        <v>4.6700000000000002E-4</v>
       </c>
       <c r="B18">
-        <v>154.09200000000001</v>
+        <v>99.126999999999995</v>
       </c>
       <c r="C18">
-        <v>-9.7399999999999993E-4</v>
+        <v>-4.0670000000000003E-3</v>
       </c>
       <c r="D18">
-        <v>-183.578</v>
+        <v>-431.44099999999997</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>1.2819999999999999E-3</v>
+        <v>8.6700000000000004E-4</v>
       </c>
       <c r="B19">
-        <v>169.81700000000001</v>
+        <v>132.82499999999999</v>
       </c>
       <c r="C19">
-        <v>-1.2819999999999999E-3</v>
+        <v>-4.4729999999999995E-3</v>
       </c>
       <c r="D19">
-        <v>-200.52500000000001</v>
+        <v>-466.87599999999998</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>1.5900000000000001E-3</v>
+        <v>1.2669999999999999E-3</v>
       </c>
       <c r="B20">
-        <v>185.69499999999999</v>
+        <v>161.59800000000001</v>
       </c>
       <c r="C20">
-        <v>-1.5900000000000001E-3</v>
+        <v>-4.921E-3</v>
       </c>
       <c r="D20">
-        <v>-217.08500000000001</v>
+        <v>-505.87400000000002</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>1.897E-3</v>
+        <v>1.6670000000000001E-3</v>
       </c>
       <c r="B21">
-        <v>201.84399999999999</v>
+        <v>189.86699999999999</v>
       </c>
       <c r="C21">
-        <v>-1.897E-3</v>
+        <v>-5.4130000000000003E-3</v>
       </c>
       <c r="D21">
-        <v>-233.64099999999999</v>
+        <v>-548.76300000000003</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>2.2049999999999999E-3</v>
+        <v>2.0670000000000003E-3</v>
       </c>
       <c r="B22">
-        <v>218.339</v>
+        <v>218.113</v>
       </c>
       <c r="C22">
-        <v>-2.2049999999999999E-3</v>
+        <v>-5.9540000000000001E-3</v>
       </c>
       <c r="D22">
-        <v>-250.40700000000001</v>
+        <v>-595.88300000000004</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>2.513E-3</v>
+        <v>2.467E-3</v>
       </c>
       <c r="B23">
-        <v>235.09899999999999</v>
+        <v>246.46700000000001</v>
       </c>
       <c r="C23">
-        <v>-2.513E-3</v>
+        <v>-6.5490000000000001E-3</v>
       </c>
       <c r="D23">
-        <v>-267.40699999999998</v>
+        <v>-647.58500000000004</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>2.8210000000000002E-3</v>
+        <v>2.8670000000000002E-3</v>
       </c>
       <c r="B24">
-        <v>252.095</v>
+        <v>275.04000000000002</v>
       </c>
       <c r="C24">
-        <v>-2.8210000000000002E-3</v>
+        <v>-7.2039999999999995E-3</v>
       </c>
       <c r="D24">
-        <v>-284.61900000000003</v>
+        <v>-704.21900000000005</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>3.1280000000000001E-3</v>
+        <v>3.2669999999999999E-3</v>
       </c>
       <c r="B25">
-        <v>269.28199999999998</v>
+        <v>303.67700000000002</v>
       </c>
       <c r="C25">
-        <v>-3.1280000000000001E-3</v>
+        <v>-7.9249999999999998E-3</v>
       </c>
       <c r="D25">
-        <v>-302.01900000000001</v>
+        <v>-764.19600000000003</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>3.441E-3</v>
+        <v>3.6669999999999997E-3</v>
       </c>
       <c r="B26">
-        <v>286.85300000000001</v>
+        <v>332.44600000000003</v>
       </c>
       <c r="C26">
-        <v>-3.441E-3</v>
+        <v>-8.7170000000000008E-3</v>
       </c>
       <c r="D26">
-        <v>-319.87200000000001</v>
+        <v>-767.09299999999996</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>3.7850000000000002E-3</v>
+        <v>4.0670000000000003E-3</v>
       </c>
       <c r="B27">
-        <v>304.87900000000002</v>
+        <v>361.32799999999997</v>
       </c>
       <c r="C27">
-        <v>-3.7850000000000002E-3</v>
+        <v>-9.5890000000000003E-3</v>
       </c>
       <c r="D27">
-        <v>-339.149</v>
+        <v>-772.13900000000001</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>4.1639999999999993E-3</v>
+        <v>4.4729999999999995E-3</v>
       </c>
       <c r="B28">
-        <v>313.548</v>
+        <v>390.767</v>
       </c>
       <c r="C28">
-        <v>-4.1639999999999993E-3</v>
+        <v>-1.0548E-2</v>
       </c>
       <c r="D28">
-        <v>-354.435</v>
+        <v>-777.98299999999995</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>4.5799999999999999E-3</v>
+        <v>4.921E-3</v>
       </c>
       <c r="B29">
-        <v>314.81799999999998</v>
+        <v>423.23099999999999</v>
       </c>
       <c r="C29">
-        <v>-4.5799999999999999E-3</v>
+        <v>-1.1603E-2</v>
       </c>
       <c r="D29">
-        <v>-355.70499999999998</v>
+        <v>-783.86599999999999</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>5.0379999999999999E-3</v>
+        <v>5.4130000000000003E-3</v>
       </c>
       <c r="B30">
-        <v>317.29000000000002</v>
+        <v>459.02300000000002</v>
       </c>
       <c r="C30">
-        <v>-5.0379999999999999E-3</v>
+        <v>-1.2763E-2</v>
       </c>
       <c r="D30">
-        <v>-357.20699999999999</v>
+        <v>-789.83699999999999</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>5.5420000000000001E-3</v>
+        <v>5.9540000000000001E-3</v>
       </c>
       <c r="B31">
-        <v>320.54899999999998</v>
+        <v>498.46800000000002</v>
       </c>
       <c r="C31">
-        <v>-5.5420000000000001E-3</v>
+        <v>-1.4038999999999999E-2</v>
       </c>
       <c r="D31">
-        <v>-359.60300000000001</v>
+        <v>-795.91099999999994</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>6.0959999999999999E-3</v>
+        <v>6.5490000000000001E-3</v>
       </c>
       <c r="B32">
-        <v>324.15499999999997</v>
+        <v>541.32799999999997</v>
       </c>
       <c r="C32">
-        <v>-6.0959999999999999E-3</v>
+        <v>-1.5443E-2</v>
       </c>
       <c r="D32">
-        <v>-363.10399999999998</v>
+        <v>-802.08199999999999</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>6.7060000000000002E-3</v>
+        <v>7.2039999999999995E-3</v>
       </c>
       <c r="B33">
-        <v>328.22800000000001</v>
+        <v>546.89400000000001</v>
       </c>
       <c r="C33">
-        <v>-6.7060000000000002E-3</v>
+        <v>-1.6986999999999999E-2</v>
       </c>
       <c r="D33">
-        <v>-366.80700000000002</v>
+        <v>-808.33299999999997</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>7.3760000000000006E-3</v>
+        <v>7.9249999999999998E-3</v>
       </c>
       <c r="B34">
-        <v>332.90899999999999</v>
+        <v>550.29200000000003</v>
       </c>
       <c r="C34">
-        <v>-7.3760000000000006E-3</v>
+        <v>-1.8686000000000001E-2</v>
       </c>
       <c r="D34">
-        <v>-370.61200000000002</v>
+        <v>-814.73099999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>8.1140000000000014E-3</v>
+        <v>8.7170000000000008E-3</v>
       </c>
       <c r="B35">
-        <v>338.10199999999998</v>
+        <v>554.83799999999997</v>
       </c>
       <c r="C35">
-        <v>-8.1140000000000014E-3</v>
+        <v>-1.9059999999999997E-2</v>
       </c>
       <c r="D35">
-        <v>-374.858</v>
+        <v>-815.94799999999998</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>8.9250000000000006E-3</v>
+        <v>9.5890000000000003E-3</v>
       </c>
       <c r="B36">
-        <v>343.76299999999998</v>
+        <v>560.72</v>
       </c>
       <c r="C36">
-        <v>-8.9250000000000006E-3</v>
+        <v>-1.9120000000000002E-2</v>
       </c>
       <c r="D36">
-        <v>-379.25099999999998</v>
+        <v>-816.28399999999999</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>9.8180000000000003E-3</v>
+        <v>1.0548E-2</v>
       </c>
       <c r="B37">
-        <v>349.96899999999999</v>
+        <v>567.68700000000001</v>
       </c>
       <c r="C37">
-        <v>-9.8180000000000003E-3</v>
+        <v>-1.9167999999999998E-2</v>
       </c>
       <c r="D37">
-        <v>-383.85700000000003</v>
+        <v>-816.45799999999997</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>1.0799E-2</v>
+        <v>1.1603E-2</v>
       </c>
       <c r="B38">
-        <v>356.40699999999998</v>
+        <v>575.49099999999999</v>
       </c>
       <c r="C38">
-        <v>-1.0799E-2</v>
+        <v>-1.9206000000000001E-2</v>
       </c>
       <c r="D38">
-        <v>-388.83499999999998</v>
+        <v>-816.59199999999998</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>1.1878999999999999E-2</v>
+        <v>1.2763E-2</v>
       </c>
       <c r="B39">
-        <v>358.94</v>
+        <v>583.928</v>
       </c>
       <c r="C39">
-        <v>-1.1878999999999999E-2</v>
+        <v>-1.9236E-2</v>
       </c>
       <c r="D39">
-        <v>-394.03399999999999</v>
+        <v>-816.70699999999999</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>1.3067E-2</v>
+        <v>1.4038999999999999E-2</v>
       </c>
       <c r="B40">
-        <v>359.346</v>
+        <v>592.88</v>
       </c>
       <c r="C40">
-        <v>-1.3067E-2</v>
+        <v>-1.9261E-2</v>
       </c>
       <c r="D40">
-        <v>-399.58</v>
+        <v>-816.80100000000004</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>1.4374000000000001E-2</v>
+        <v>1.5443E-2</v>
       </c>
       <c r="B41">
-        <v>359.41800000000001</v>
+        <v>602.25599999999997</v>
       </c>
       <c r="C41">
-        <v>-1.4374000000000001E-2</v>
+        <v>-1.9281E-2</v>
       </c>
       <c r="D41">
-        <v>-405.399</v>
+        <v>-816.87</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>1.5810999999999999E-2</v>
+        <v>1.6986999999999999E-2</v>
       </c>
       <c r="B42">
-        <v>359.31400000000002</v>
+        <v>609.88900000000001</v>
       </c>
       <c r="C42">
-        <v>-1.5810999999999999E-2</v>
+        <v>-1.9359000000000001E-2</v>
       </c>
       <c r="D42">
-        <v>-411.58</v>
+        <v>-817.12400000000002</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>1.7393000000000002E-2</v>
+        <v>1.8686000000000001E-2</v>
       </c>
       <c r="B43">
-        <v>359.05700000000002</v>
+        <v>615.24400000000003</v>
       </c>
       <c r="C43">
-        <v>-1.7393000000000002E-2</v>
+        <v>-2.0555E-2</v>
       </c>
       <c r="D43">
-        <v>-417.98399999999998</v>
+        <v>-821.15800000000002</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>1.9132000000000003E-2</v>
+        <v>2.0555E-2</v>
       </c>
       <c r="B44">
-        <v>358.83800000000002</v>
+        <v>617.95600000000002</v>
       </c>
       <c r="C44">
-        <v>-1.9132000000000003E-2</v>
+        <v>-2.2609999999999998E-2</v>
       </c>
       <c r="D44">
-        <v>-423.33600000000001</v>
+        <v>-827.33900000000006</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>2.1045000000000001E-2</v>
+        <v>2.2609999999999998E-2</v>
       </c>
       <c r="B45">
-        <v>358.596</v>
+        <v>620.57799999999997</v>
       </c>
       <c r="C45">
-        <v>-2.1045000000000001E-2</v>
+        <v>-2.4870999999999997E-2</v>
       </c>
       <c r="D45">
-        <v>-422.483</v>
+        <v>-833.18899999999996</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>2.3148999999999999E-2</v>
+        <v>2.4870999999999997E-2</v>
       </c>
       <c r="B46">
-        <v>358.59500000000003</v>
+        <v>623.452</v>
       </c>
       <c r="C46">
-        <v>-2.3148999999999999E-2</v>
+        <v>-2.7358E-2</v>
       </c>
       <c r="D46">
-        <v>-421.26499999999999</v>
+        <v>-838.15800000000002</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>2.5463999999999997E-2</v>
+        <v>2.7358E-2</v>
       </c>
       <c r="B47">
-        <v>358.49599999999998</v>
+        <v>626.15099999999995</v>
       </c>
       <c r="C47">
-        <v>-2.3242000000000002E-2</v>
+        <v>-3.0094000000000003E-2</v>
       </c>
       <c r="D47">
-        <v>-421.21800000000002</v>
+        <v>-841.26900000000001</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>2.8010999999999998E-2</v>
+        <v>3.0094000000000003E-2</v>
       </c>
       <c r="B48">
-        <v>361.98700000000002</v>
+        <v>629.048</v>
       </c>
       <c r="C48">
-        <v>-2.3316E-2</v>
+        <v>-3.3104000000000001E-2</v>
       </c>
       <c r="D48">
-        <v>-421.13799999999998</v>
+        <v>-838.93799999999999</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>3.0812000000000003E-2</v>
+        <v>3.3104000000000001E-2</v>
       </c>
       <c r="B49">
-        <v>366.26299999999998</v>
+        <v>631.875</v>
       </c>
       <c r="C49">
-        <v>-2.3611999999999998E-2</v>
+        <v>-3.6414000000000002E-2</v>
       </c>
       <c r="D49">
-        <v>-421.01400000000001</v>
+        <v>-833.84199999999998</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>3.3893E-2</v>
+        <v>3.3765999999999997E-2</v>
       </c>
       <c r="B50">
-        <v>371.024</v>
+        <v>632.43200000000002</v>
       </c>
       <c r="C50">
-        <v>-2.5463999999999997E-2</v>
+        <v>-4.0055999999999994E-2</v>
       </c>
       <c r="D50">
-        <v>-419.8</v>
+        <v>-828.95299999999997</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>3.7283000000000004E-2</v>
+        <v>3.4296E-2</v>
       </c>
       <c r="B51">
-        <v>376.22199999999998</v>
+        <v>632.89700000000005</v>
       </c>
       <c r="C51">
-        <v>-2.8010999999999998E-2</v>
+        <v>-4.4061000000000003E-2</v>
       </c>
       <c r="D51">
-        <v>-419.25900000000001</v>
+        <v>-827.70600000000002</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>4.1011000000000006E-2</v>
+        <v>3.4380000000000001E-2</v>
       </c>
       <c r="B52">
-        <v>381.99200000000002</v>
+        <v>632.94799999999998</v>
       </c>
       <c r="C52">
-        <v>-3.0812000000000003E-2</v>
+        <v>-4.8466999999999996E-2</v>
       </c>
       <c r="D52">
-        <v>-421.23500000000001</v>
+        <v>-828.05700000000002</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>4.5111999999999999E-2</v>
+        <v>3.4447999999999999E-2</v>
       </c>
       <c r="B53">
-        <v>388.05500000000001</v>
+        <v>633.03</v>
       </c>
       <c r="C53">
-        <v>-3.3893E-2</v>
+        <v>-5.3314E-2</v>
       </c>
       <c r="D53">
-        <v>-423.39499999999998</v>
+        <v>-820.46799999999996</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>4.9623E-2</v>
+        <v>3.4719E-2</v>
       </c>
       <c r="B54">
-        <v>394.63600000000002</v>
+        <v>633.13599999999997</v>
       </c>
       <c r="C54">
-        <v>-3.7283000000000004E-2</v>
+        <v>-5.8645000000000003E-2</v>
       </c>
       <c r="D54">
-        <v>-425.601</v>
+        <v>-814.08500000000004</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>5.0615E-2</v>
+        <v>3.6414000000000002E-2</v>
       </c>
       <c r="B55">
-        <v>396.03800000000001</v>
+        <v>635.70399999999995</v>
       </c>
       <c r="C55">
-        <v>-4.1011000000000006E-2</v>
+        <v>-6.4510000000000012E-2</v>
       </c>
       <c r="D55">
-        <v>-427.76400000000001</v>
+        <v>-809.86800000000005</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>5.1408999999999996E-2</v>
+        <v>4.0055999999999994E-2</v>
       </c>
       <c r="B56">
-        <v>397.21</v>
+        <v>642.32799999999997</v>
       </c>
       <c r="C56">
-        <v>-4.5111999999999999E-2</v>
+        <v>-7.0960999999999996E-2</v>
       </c>
       <c r="D56">
-        <v>-430.13200000000001</v>
+        <v>-809.21</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>5.1535999999999998E-2</v>
+        <v>4.4061000000000003E-2</v>
       </c>
       <c r="B57">
-        <v>397.387</v>
-      </c>
-      <c r="C57">
-        <v>-4.9623E-2</v>
-      </c>
-      <c r="D57">
-        <v>-432.47699999999998</v>
+        <v>650.57899999999995</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>5.1637999999999996E-2</v>
+        <v>4.8466999999999996E-2</v>
       </c>
       <c r="B58">
-        <v>397.50099999999998</v>
-      </c>
-      <c r="C58">
-        <v>-5.4585000000000002E-2</v>
-      </c>
-      <c r="D58">
-        <v>-434.67599999999999</v>
+        <v>657.83900000000006</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>5.1719000000000001E-2</v>
+        <v>5.3314E-2</v>
       </c>
       <c r="B59">
-        <v>397.613</v>
-      </c>
-      <c r="C59">
-        <v>-6.0044E-2</v>
-      </c>
-      <c r="D59">
-        <v>-436.88</v>
+        <v>663.24199999999996</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>5.1783999999999997E-2</v>
+        <v>5.8645000000000003E-2</v>
       </c>
       <c r="B60">
-        <v>397.70400000000001</v>
-      </c>
-      <c r="C60">
-        <v>-6.6047999999999996E-2</v>
-      </c>
-      <c r="D60">
-        <v>-439.185</v>
+        <v>666.53099999999995</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>5.2045000000000001E-2</v>
+        <v>6.4510000000000012E-2</v>
       </c>
       <c r="B61">
-        <v>398.09</v>
-      </c>
-      <c r="C61">
-        <v>-7.2653000000000009E-2</v>
-      </c>
-      <c r="D61">
-        <v>-441.81200000000001</v>
+        <v>668.06700000000001</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>5.4585000000000002E-2</v>
+        <v>7.0960999999999996E-2</v>
       </c>
       <c r="B62">
-        <v>401.59699999999998</v>
-      </c>
-      <c r="C62">
-        <v>-7.9918000000000003E-2</v>
-      </c>
-      <c r="D62">
-        <v>-444.75099999999998</v>
+        <v>668.81299999999999</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>6.0044E-2</v>
+        <v>7.8057000000000001E-2</v>
       </c>
       <c r="B63">
-        <v>408.43700000000001</v>
-      </c>
-      <c r="C63">
-        <v>-8.1516999999999992E-2</v>
-      </c>
-      <c r="D63">
-        <v>-445.48</v>
+        <v>669.654</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>6.0283999999999997E-2</v>
+        <v>8.5862999999999995E-2</v>
       </c>
       <c r="B64">
-        <v>408.64100000000002</v>
-      </c>
-      <c r="C64">
-        <v>-8.3275000000000002E-2</v>
-      </c>
-      <c r="D64">
-        <v>-446.113</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+        <v>672.12599999999998</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>6.0548000000000005E-2</v>
+        <v>9.4448999999999991E-2</v>
       </c>
       <c r="B65">
-        <v>408.92500000000001</v>
-      </c>
-      <c r="C65">
-        <v>-8.3450999999999997E-2</v>
-      </c>
-      <c r="D65">
-        <v>-446.06400000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+        <v>676.94200000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>6.0816000000000002E-2</v>
+        <v>0.103894</v>
       </c>
       <c r="B66">
-        <v>409.20800000000003</v>
-      </c>
-      <c r="C66">
-        <v>-8.3630999999999997E-2</v>
-      </c>
-      <c r="D66">
-        <v>-446.15100000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C67">
-        <v>-8.3811999999999998E-2</v>
-      </c>
-      <c r="D67">
-        <v>-446.32400000000001</v>
+        <v>680.38099999999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>0.114283</v>
+      </c>
+      <c r="B67">
+        <v>679.11500000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2313,7 +3140,1857 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D755C19-D8E9-42D1-A154-69EF42E6944D}">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="10.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>6.7000000000000002E-5</v>
+      </c>
+      <c r="B5">
+        <v>12.317</v>
+      </c>
+      <c r="C5">
+        <v>-6.7000000000000002E-5</v>
+      </c>
+      <c r="D5">
+        <v>-12.311999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1.47E-4</v>
+      </c>
+      <c r="B6">
+        <v>27.096</v>
+      </c>
+      <c r="C6">
+        <v>-4.6700000000000002E-4</v>
+      </c>
+      <c r="D6">
+        <v>-86.182000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2.1100000000000001E-4</v>
+      </c>
+      <c r="B7">
+        <v>38.92</v>
+      </c>
+      <c r="C7">
+        <v>-4.8299999999999998E-4</v>
+      </c>
+      <c r="D7">
+        <v>-89.135999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2.6200000000000003E-4</v>
+      </c>
+      <c r="B8">
+        <v>48.378999999999998</v>
+      </c>
+      <c r="C8">
+        <v>-4.95E-4</v>
+      </c>
+      <c r="D8">
+        <v>-91.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>3.0299999999999999E-4</v>
+      </c>
+      <c r="B9">
+        <v>55.947000000000003</v>
+      </c>
+      <c r="C9">
+        <v>-5.0600000000000005E-4</v>
+      </c>
+      <c r="D9">
+        <v>-93.391000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>3.0899999999999998E-4</v>
+      </c>
+      <c r="B10">
+        <v>57.156999999999996</v>
+      </c>
+      <c r="C10">
+        <v>-5.1400000000000003E-4</v>
+      </c>
+      <c r="D10">
+        <v>-83.912000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>3.1500000000000001E-4</v>
+      </c>
+      <c r="B11">
+        <v>58.125999999999998</v>
+      </c>
+      <c r="C11">
+        <v>-5.4700000000000007E-4</v>
+      </c>
+      <c r="D11">
+        <v>-84.772999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>3.19E-4</v>
+      </c>
+      <c r="B12">
+        <v>58.901000000000003</v>
+      </c>
+      <c r="C12">
+        <v>-8.6700000000000004E-4</v>
+      </c>
+      <c r="D12">
+        <v>-104.88500000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>3.2200000000000002E-4</v>
+      </c>
+      <c r="B13">
+        <v>59.521000000000001</v>
+      </c>
+      <c r="C13">
+        <v>-1.2669999999999999E-3</v>
+      </c>
+      <c r="D13">
+        <v>-126.30800000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>3.2499999999999999E-4</v>
+      </c>
+      <c r="B14">
+        <v>60.017000000000003</v>
+      </c>
+      <c r="C14">
+        <v>-1.6670000000000001E-3</v>
+      </c>
+      <c r="D14">
+        <v>-146.886</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>3.2700000000000003E-4</v>
+      </c>
+      <c r="B15">
+        <v>60.412999999999997</v>
+      </c>
+      <c r="C15">
+        <v>-2.0670000000000003E-3</v>
+      </c>
+      <c r="D15">
+        <v>-167.374</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>3.2900000000000003E-4</v>
+      </c>
+      <c r="B16">
+        <v>60.731000000000002</v>
+      </c>
+      <c r="C16">
+        <v>-2.467E-3</v>
+      </c>
+      <c r="D16">
+        <v>-187.90899999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>3.3E-4</v>
+      </c>
+      <c r="B17">
+        <v>60.984000000000002</v>
+      </c>
+      <c r="C17">
+        <v>-2.8670000000000002E-3</v>
+      </c>
+      <c r="D17">
+        <v>-208.53299999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>3.3600000000000004E-4</v>
+      </c>
+      <c r="B18">
+        <v>60.985999999999997</v>
+      </c>
+      <c r="C18">
+        <v>-3.2669999999999999E-3</v>
+      </c>
+      <c r="D18">
+        <v>-229.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>4.6700000000000002E-4</v>
+      </c>
+      <c r="B19">
+        <v>67.156999999999996</v>
+      </c>
+      <c r="C19">
+        <v>-3.6669999999999997E-3</v>
+      </c>
+      <c r="D19">
+        <v>-250.04300000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>8.6700000000000004E-4</v>
+      </c>
+      <c r="B20">
+        <v>92.11</v>
+      </c>
+      <c r="C20">
+        <v>-4.0670000000000003E-3</v>
+      </c>
+      <c r="D20">
+        <v>-270.89800000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1.2669999999999999E-3</v>
+      </c>
+      <c r="B21">
+        <v>114.93899999999999</v>
+      </c>
+      <c r="C21">
+        <v>-4.4729999999999995E-3</v>
+      </c>
+      <c r="D21">
+        <v>-292.14400000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1.6670000000000001E-3</v>
+      </c>
+      <c r="B22">
+        <v>137.65</v>
+      </c>
+      <c r="C22">
+        <v>-4.921E-3</v>
+      </c>
+      <c r="D22">
+        <v>-315.55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2.0670000000000003E-3</v>
+      </c>
+      <c r="B23">
+        <v>160.41800000000001</v>
+      </c>
+      <c r="C23">
+        <v>-5.4130000000000003E-3</v>
+      </c>
+      <c r="D23">
+        <v>-341.32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2.467E-3</v>
+      </c>
+      <c r="B24">
+        <v>183.304</v>
+      </c>
+      <c r="C24">
+        <v>-5.9540000000000001E-3</v>
+      </c>
+      <c r="D24">
+        <v>-369.66199999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2.8670000000000002E-3</v>
+      </c>
+      <c r="B25">
+        <v>206.28</v>
+      </c>
+      <c r="C25">
+        <v>-6.5490000000000001E-3</v>
+      </c>
+      <c r="D25">
+        <v>-400.80099999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3.2669999999999999E-3</v>
+      </c>
+      <c r="B26">
+        <v>229.35400000000001</v>
+      </c>
+      <c r="C26">
+        <v>-7.2039999999999995E-3</v>
+      </c>
+      <c r="D26">
+        <v>-434.95600000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3.6669999999999997E-3</v>
+      </c>
+      <c r="B27">
+        <v>252.48599999999999</v>
+      </c>
+      <c r="C27">
+        <v>-7.9249999999999998E-3</v>
+      </c>
+      <c r="D27">
+        <v>-454.61200000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>4.0670000000000003E-3</v>
+      </c>
+      <c r="B28">
+        <v>275.68099999999998</v>
+      </c>
+      <c r="C28">
+        <v>-8.7170000000000008E-3</v>
+      </c>
+      <c r="D28">
+        <v>-457.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>4.4729999999999995E-3</v>
+      </c>
+      <c r="B29">
+        <v>299.31299999999999</v>
+      </c>
+      <c r="C29">
+        <v>-9.5890000000000003E-3</v>
+      </c>
+      <c r="D29">
+        <v>-460.32499999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4.921E-3</v>
+      </c>
+      <c r="B30">
+        <v>325.35500000000002</v>
+      </c>
+      <c r="C30">
+        <v>-1.0548E-2</v>
+      </c>
+      <c r="D30">
+        <v>-463.73099999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>5.4130000000000003E-3</v>
+      </c>
+      <c r="B31">
+        <v>354.04599999999999</v>
+      </c>
+      <c r="C31">
+        <v>-1.1603E-2</v>
+      </c>
+      <c r="D31">
+        <v>-467.18799999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>5.9540000000000001E-3</v>
+      </c>
+      <c r="B32">
+        <v>385.64800000000002</v>
+      </c>
+      <c r="C32">
+        <v>-1.2763E-2</v>
+      </c>
+      <c r="D32">
+        <v>-470.72899999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>6.5490000000000001E-3</v>
+      </c>
+      <c r="B33">
+        <v>420.42700000000002</v>
+      </c>
+      <c r="C33">
+        <v>-1.4038999999999999E-2</v>
+      </c>
+      <c r="D33">
+        <v>-474.35399999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>7.2039999999999995E-3</v>
+      </c>
+      <c r="B34">
+        <v>428.548</v>
+      </c>
+      <c r="C34">
+        <v>-1.5443E-2</v>
+      </c>
+      <c r="D34">
+        <v>-478.07799999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>7.9249999999999998E-3</v>
+      </c>
+      <c r="B35">
+        <v>431.13400000000001</v>
+      </c>
+      <c r="C35">
+        <v>-1.6986999999999999E-2</v>
+      </c>
+      <c r="D35">
+        <v>-481.88299999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>8.7170000000000008E-3</v>
+      </c>
+      <c r="B36">
+        <v>434.38799999999998</v>
+      </c>
+      <c r="C36">
+        <v>-1.8686000000000001E-2</v>
+      </c>
+      <c r="D36">
+        <v>-485.72199999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>9.5890000000000003E-3</v>
+      </c>
+      <c r="B37">
+        <v>438.24400000000003</v>
+      </c>
+      <c r="C37">
+        <v>-1.9059999999999997E-2</v>
+      </c>
+      <c r="D37">
+        <v>-486.62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1.0548E-2</v>
+      </c>
+      <c r="B38">
+        <v>442.649</v>
+      </c>
+      <c r="C38">
+        <v>-1.9359000000000001E-2</v>
+      </c>
+      <c r="D38">
+        <v>-487.286</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1.1603E-2</v>
+      </c>
+      <c r="B39">
+        <v>447.61500000000001</v>
+      </c>
+      <c r="C39">
+        <v>-1.9597999999999997E-2</v>
+      </c>
+      <c r="D39">
+        <v>-487.774</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1.2763E-2</v>
+      </c>
+      <c r="B40">
+        <v>452.91699999999997</v>
+      </c>
+      <c r="C40">
+        <v>-1.9789000000000001E-2</v>
+      </c>
+      <c r="D40">
+        <v>-488.17099999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1.4038999999999999E-2</v>
+      </c>
+      <c r="B41">
+        <v>458.54</v>
+      </c>
+      <c r="C41">
+        <v>-1.9943000000000002E-2</v>
+      </c>
+      <c r="D41">
+        <v>-488.48099999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>1.5443E-2</v>
+      </c>
+      <c r="B42">
+        <v>464.24400000000003</v>
+      </c>
+      <c r="C42">
+        <v>-2.0065000000000003E-2</v>
+      </c>
+      <c r="D42">
+        <v>-488.76499999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1.6986999999999999E-2</v>
+      </c>
+      <c r="B43">
+        <v>468.95299999999997</v>
+      </c>
+      <c r="C43">
+        <v>-2.0163E-2</v>
+      </c>
+      <c r="D43">
+        <v>-488.97699999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1.8686000000000001E-2</v>
+      </c>
+      <c r="B44">
+        <v>472.55099999999999</v>
+      </c>
+      <c r="C44">
+        <v>-2.0240999999999999E-2</v>
+      </c>
+      <c r="D44">
+        <v>-489.16500000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>2.0555E-2</v>
+      </c>
+      <c r="B45">
+        <v>474.52699999999999</v>
+      </c>
+      <c r="C45">
+        <v>-2.0303999999999999E-2</v>
+      </c>
+      <c r="D45">
+        <v>-489.29899999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>2.2609999999999998E-2</v>
+      </c>
+      <c r="B46">
+        <v>476.31</v>
+      </c>
+      <c r="C46">
+        <v>-2.0354000000000001E-2</v>
+      </c>
+      <c r="D46">
+        <v>-489.42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>2.4870999999999997E-2</v>
+      </c>
+      <c r="B47">
+        <v>478.12400000000002</v>
+      </c>
+      <c r="C47">
+        <v>-2.0393999999999999E-2</v>
+      </c>
+      <c r="D47">
+        <v>-489.50700000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>2.7358E-2</v>
+      </c>
+      <c r="B48">
+        <v>480.01600000000002</v>
+      </c>
+      <c r="C48">
+        <v>-2.0555E-2</v>
+      </c>
+      <c r="D48">
+        <v>-489.82299999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>3.0094000000000003E-2</v>
+      </c>
+      <c r="B49">
+        <v>481.858</v>
+      </c>
+      <c r="C49">
+        <v>-2.2609999999999998E-2</v>
+      </c>
+      <c r="D49">
+        <v>-493.899</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>3.3104000000000001E-2</v>
+      </c>
+      <c r="B50">
+        <v>483.58</v>
+      </c>
+      <c r="C50">
+        <v>-2.4870999999999997E-2</v>
+      </c>
+      <c r="D50">
+        <v>-497.86900000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>3.6414000000000002E-2</v>
+      </c>
+      <c r="B51">
+        <v>486.87099999999998</v>
+      </c>
+      <c r="C51">
+        <v>-2.7358E-2</v>
+      </c>
+      <c r="D51">
+        <v>-501.59300000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>3.7142000000000001E-2</v>
+      </c>
+      <c r="B52">
+        <v>487.92700000000002</v>
+      </c>
+      <c r="C52">
+        <v>-3.0094000000000003E-2</v>
+      </c>
+      <c r="D52">
+        <v>-504.971</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>3.7725000000000002E-2</v>
+      </c>
+      <c r="B53">
+        <v>488.89499999999998</v>
+      </c>
+      <c r="C53">
+        <v>-3.3104000000000001E-2</v>
+      </c>
+      <c r="D53">
+        <v>-507.197</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>3.7817999999999997E-2</v>
+      </c>
+      <c r="B54">
+        <v>489.02100000000002</v>
+      </c>
+      <c r="C54">
+        <v>-3.6414000000000002E-2</v>
+      </c>
+      <c r="D54">
+        <v>-505.72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>3.7893000000000003E-2</v>
+      </c>
+      <c r="B55">
+        <v>489.14400000000001</v>
+      </c>
+      <c r="C55">
+        <v>-4.0055999999999994E-2</v>
+      </c>
+      <c r="D55">
+        <v>-504.387</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>3.7953000000000001E-2</v>
+      </c>
+      <c r="B56">
+        <v>489.24099999999999</v>
+      </c>
+      <c r="C56">
+        <v>-4.4061000000000003E-2</v>
+      </c>
+      <c r="D56">
+        <v>-505.149</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="B57">
+        <v>489.30200000000002</v>
+      </c>
+      <c r="C57">
+        <v>-4.8466999999999996E-2</v>
+      </c>
+      <c r="D57">
+        <v>-507.73099999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>3.8191000000000003E-2</v>
+      </c>
+      <c r="B58">
+        <v>489.53899999999999</v>
+      </c>
+      <c r="C58">
+        <v>-5.3314E-2</v>
+      </c>
+      <c r="D58">
+        <v>-511.17200000000003</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>4.0055999999999994E-2</v>
+      </c>
+      <c r="B59">
+        <v>492.70699999999999</v>
+      </c>
+      <c r="C59">
+        <v>-5.8645000000000003E-2</v>
+      </c>
+      <c r="D59">
+        <v>-511.65100000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>4.4061000000000003E-2</v>
+      </c>
+      <c r="B60">
+        <v>499.99299999999999</v>
+      </c>
+      <c r="C60">
+        <v>-6.4510000000000012E-2</v>
+      </c>
+      <c r="D60">
+        <v>-510.80500000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>4.8466999999999996E-2</v>
+      </c>
+      <c r="B61">
+        <v>506.99200000000002</v>
+      </c>
+      <c r="C61">
+        <v>-7.0960999999999996E-2</v>
+      </c>
+      <c r="D61">
+        <v>-510.98200000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>5.3314E-2</v>
+      </c>
+      <c r="B62">
+        <v>513.21699999999998</v>
+      </c>
+      <c r="C62">
+        <v>-7.8057000000000001E-2</v>
+      </c>
+      <c r="D62">
+        <v>-512.46500000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>5.8645000000000003E-2</v>
+      </c>
+      <c r="B63">
+        <v>518.14099999999996</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>6.4510000000000012E-2</v>
+      </c>
+      <c r="B64">
+        <v>521.27099999999996</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>7.0960999999999996E-2</v>
+      </c>
+      <c r="B65">
+        <v>522.90099999999995</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>7.8057000000000001E-2</v>
+      </c>
+      <c r="B66">
+        <v>523.61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>8.5862999999999995E-2</v>
+      </c>
+      <c r="B67">
+        <v>524.25199999999995</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>9.4448999999999991E-2</v>
+      </c>
+      <c r="B68">
+        <v>525.92600000000004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>0.103894</v>
+      </c>
+      <c r="B69">
+        <v>529.44200000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>0.114283</v>
+      </c>
+      <c r="B70">
+        <v>531.50099999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>0.12571199999999999</v>
+      </c>
+      <c r="B71">
+        <v>530.43700000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{459C6E40-54AF-40EA-9100-731006E4B0B6}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>6.7000000000000002E-5</v>
+      </c>
+      <c r="B5">
+        <v>12.2</v>
+      </c>
+      <c r="C5">
+        <v>-6.7000000000000002E-5</v>
+      </c>
+      <c r="D5">
+        <v>-12.196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1.47E-4</v>
+      </c>
+      <c r="B6">
+        <v>26.84</v>
+      </c>
+      <c r="C6">
+        <v>-4.6700000000000002E-4</v>
+      </c>
+      <c r="D6">
+        <v>-85.367999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2.1100000000000001E-4</v>
+      </c>
+      <c r="B7">
+        <v>38.552999999999997</v>
+      </c>
+      <c r="C7">
+        <v>-4.8299999999999998E-4</v>
+      </c>
+      <c r="D7">
+        <v>-88.295000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2.6200000000000003E-4</v>
+      </c>
+      <c r="B8">
+        <v>47.921999999999997</v>
+      </c>
+      <c r="C8">
+        <v>-4.95E-4</v>
+      </c>
+      <c r="D8">
+        <v>-90.635999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>3.0299999999999999E-4</v>
+      </c>
+      <c r="B9">
+        <v>55.417999999999999</v>
+      </c>
+      <c r="C9">
+        <v>-5.0600000000000005E-4</v>
+      </c>
+      <c r="D9">
+        <v>-92.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>3.0899999999999998E-4</v>
+      </c>
+      <c r="B10">
+        <v>56.616999999999997</v>
+      </c>
+      <c r="C10">
+        <v>-5.1400000000000003E-4</v>
+      </c>
+      <c r="D10">
+        <v>-82.271000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>3.1500000000000001E-4</v>
+      </c>
+      <c r="B11">
+        <v>57.576999999999998</v>
+      </c>
+      <c r="C11">
+        <v>-5.4700000000000007E-4</v>
+      </c>
+      <c r="D11">
+        <v>-83.715000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>3.19E-4</v>
+      </c>
+      <c r="B12">
+        <v>58.344000000000001</v>
+      </c>
+      <c r="C12">
+        <v>-8.6700000000000004E-4</v>
+      </c>
+      <c r="D12">
+        <v>-103.84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>3.2200000000000002E-4</v>
+      </c>
+      <c r="B13">
+        <v>58.957999999999998</v>
+      </c>
+      <c r="C13">
+        <v>-1.2669999999999999E-3</v>
+      </c>
+      <c r="D13">
+        <v>-125.267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>3.2499999999999999E-4</v>
+      </c>
+      <c r="B14">
+        <v>59.45</v>
+      </c>
+      <c r="C14">
+        <v>-1.6670000000000001E-3</v>
+      </c>
+      <c r="D14">
+        <v>-145.874</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>3.2700000000000003E-4</v>
+      </c>
+      <c r="B15">
+        <v>59.841999999999999</v>
+      </c>
+      <c r="C15">
+        <v>-2.0670000000000003E-3</v>
+      </c>
+      <c r="D15">
+        <v>-166.386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>3.2900000000000003E-4</v>
+      </c>
+      <c r="B16">
+        <v>60.156999999999996</v>
+      </c>
+      <c r="C16">
+        <v>-2.467E-3</v>
+      </c>
+      <c r="D16">
+        <v>-186.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>3.3E-4</v>
+      </c>
+      <c r="B17">
+        <v>60.408999999999999</v>
+      </c>
+      <c r="C17">
+        <v>-2.8670000000000002E-3</v>
+      </c>
+      <c r="D17">
+        <v>-207.61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>3.3600000000000004E-4</v>
+      </c>
+      <c r="B18">
+        <v>61.115000000000002</v>
+      </c>
+      <c r="C18">
+        <v>-3.2669999999999999E-3</v>
+      </c>
+      <c r="D18">
+        <v>-228.351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>4.6700000000000002E-4</v>
+      </c>
+      <c r="B19">
+        <v>66.759</v>
+      </c>
+      <c r="C19">
+        <v>-3.6669999999999997E-3</v>
+      </c>
+      <c r="D19">
+        <v>-249.167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>8.6700000000000004E-4</v>
+      </c>
+      <c r="B20">
+        <v>91.673000000000002</v>
+      </c>
+      <c r="C20">
+        <v>-4.0670000000000003E-3</v>
+      </c>
+      <c r="D20">
+        <v>-270.04300000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1.2669999999999999E-3</v>
+      </c>
+      <c r="B21">
+        <v>114.422</v>
+      </c>
+      <c r="C21">
+        <v>-4.4729999999999995E-3</v>
+      </c>
+      <c r="D21">
+        <v>-291.31200000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1.6670000000000001E-3</v>
+      </c>
+      <c r="B22">
+        <v>137.04</v>
+      </c>
+      <c r="C22">
+        <v>-4.921E-3</v>
+      </c>
+      <c r="D22">
+        <v>-314.738</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2.0670000000000003E-3</v>
+      </c>
+      <c r="B23">
+        <v>159.733</v>
+      </c>
+      <c r="C23">
+        <v>-5.4130000000000003E-3</v>
+      </c>
+      <c r="D23">
+        <v>-340.52600000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2.467E-3</v>
+      </c>
+      <c r="B24">
+        <v>182.523</v>
+      </c>
+      <c r="C24">
+        <v>-5.9540000000000001E-3</v>
+      </c>
+      <c r="D24">
+        <v>-368.88900000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2.8670000000000002E-3</v>
+      </c>
+      <c r="B25">
+        <v>205.41200000000001</v>
+      </c>
+      <c r="C25">
+        <v>-6.5490000000000001E-3</v>
+      </c>
+      <c r="D25">
+        <v>-400.04899999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3.2669999999999999E-3</v>
+      </c>
+      <c r="B26">
+        <v>228.38499999999999</v>
+      </c>
+      <c r="C26">
+        <v>-7.2039999999999995E-3</v>
+      </c>
+      <c r="D26">
+        <v>-434.22699999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3.6669999999999997E-3</v>
+      </c>
+      <c r="B27">
+        <v>251.43</v>
+      </c>
+      <c r="C27">
+        <v>-7.9249999999999998E-3</v>
+      </c>
+      <c r="D27">
+        <v>-454.57100000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>4.0670000000000003E-3</v>
+      </c>
+      <c r="B28">
+        <v>274.53199999999998</v>
+      </c>
+      <c r="C28">
+        <v>-8.7170000000000008E-3</v>
+      </c>
+      <c r="D28">
+        <v>-456.94299999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>4.4729999999999995E-3</v>
+      </c>
+      <c r="B29">
+        <v>298.06900000000002</v>
+      </c>
+      <c r="C29">
+        <v>-9.5890000000000003E-3</v>
+      </c>
+      <c r="D29">
+        <v>-460.20100000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4.921E-3</v>
+      </c>
+      <c r="B30">
+        <v>324.00599999999997</v>
+      </c>
+      <c r="C30">
+        <v>-1.0548E-2</v>
+      </c>
+      <c r="D30">
+        <v>-463.58199999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>5.4130000000000003E-3</v>
+      </c>
+      <c r="B31">
+        <v>352.58100000000002</v>
+      </c>
+      <c r="C31">
+        <v>-1.1603E-2</v>
+      </c>
+      <c r="D31">
+        <v>-467.03199999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>5.9540000000000001E-3</v>
+      </c>
+      <c r="B32">
+        <v>384.05399999999997</v>
+      </c>
+      <c r="C32">
+        <v>-1.2763E-2</v>
+      </c>
+      <c r="D32">
+        <v>-470.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>6.5490000000000001E-3</v>
+      </c>
+      <c r="B33">
+        <v>418.70400000000001</v>
+      </c>
+      <c r="C33">
+        <v>-1.4038999999999999E-2</v>
+      </c>
+      <c r="D33">
+        <v>-474.15800000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>7.2039999999999995E-3</v>
+      </c>
+      <c r="B34">
+        <v>427.94299999999998</v>
+      </c>
+      <c r="C34">
+        <v>-1.5443E-2</v>
+      </c>
+      <c r="D34">
+        <v>-477.858</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>7.9249999999999998E-3</v>
+      </c>
+      <c r="B35">
+        <v>430.464</v>
+      </c>
+      <c r="C35">
+        <v>-1.6986999999999999E-2</v>
+      </c>
+      <c r="D35">
+        <v>-481.64299999999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>8.7170000000000008E-3</v>
+      </c>
+      <c r="B36">
+        <v>433.60700000000003</v>
+      </c>
+      <c r="C36">
+        <v>-1.8686000000000001E-2</v>
+      </c>
+      <c r="D36">
+        <v>-485.46199999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>9.5890000000000003E-3</v>
+      </c>
+      <c r="B37">
+        <v>437.315</v>
+      </c>
+      <c r="C37">
+        <v>-1.9059999999999997E-2</v>
+      </c>
+      <c r="D37">
+        <v>-486.36799999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1.0548E-2</v>
+      </c>
+      <c r="B38">
+        <v>441.59300000000002</v>
+      </c>
+      <c r="C38">
+        <v>-1.9359000000000001E-2</v>
+      </c>
+      <c r="D38">
+        <v>-487.00599999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1.1603E-2</v>
+      </c>
+      <c r="B39">
+        <v>446.44099999999997</v>
+      </c>
+      <c r="C39">
+        <v>-1.9597999999999997E-2</v>
+      </c>
+      <c r="D39">
+        <v>-487.524</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1.2763E-2</v>
+      </c>
+      <c r="B40">
+        <v>451.72199999999998</v>
+      </c>
+      <c r="C40">
+        <v>-1.9789000000000001E-2</v>
+      </c>
+      <c r="D40">
+        <v>-487.90800000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1.4038999999999999E-2</v>
+      </c>
+      <c r="B41">
+        <v>457.23200000000003</v>
+      </c>
+      <c r="C41">
+        <v>-1.9943000000000002E-2</v>
+      </c>
+      <c r="D41">
+        <v>-488.20100000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>1.5443E-2</v>
+      </c>
+      <c r="B42">
+        <v>463.1</v>
+      </c>
+      <c r="C42">
+        <v>-2.0065000000000003E-2</v>
+      </c>
+      <c r="D42">
+        <v>-488.48500000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1.6986999999999999E-2</v>
+      </c>
+      <c r="B43">
+        <v>467.95600000000002</v>
+      </c>
+      <c r="C43">
+        <v>-2.0163E-2</v>
+      </c>
+      <c r="D43">
+        <v>-488.697</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1.8686000000000001E-2</v>
+      </c>
+      <c r="B44">
+        <v>471.68900000000002</v>
+      </c>
+      <c r="C44">
+        <v>-2.0240999999999999E-2</v>
+      </c>
+      <c r="D44">
+        <v>-488.87700000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>2.0555E-2</v>
+      </c>
+      <c r="B45">
+        <v>473.78699999999998</v>
+      </c>
+      <c r="C45">
+        <v>-2.0303999999999999E-2</v>
+      </c>
+      <c r="D45">
+        <v>-489.01299999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>2.2609999999999998E-2</v>
+      </c>
+      <c r="B46">
+        <v>475.56799999999998</v>
+      </c>
+      <c r="C46">
+        <v>-2.0354000000000001E-2</v>
+      </c>
+      <c r="D46">
+        <v>-489.12900000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>2.4870999999999997E-2</v>
+      </c>
+      <c r="B47">
+        <v>477.35300000000001</v>
+      </c>
+      <c r="C47">
+        <v>-2.0393999999999999E-2</v>
+      </c>
+      <c r="D47">
+        <v>-489.21899999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>2.7358E-2</v>
+      </c>
+      <c r="B48">
+        <v>479.17599999999999</v>
+      </c>
+      <c r="C48">
+        <v>-2.0555E-2</v>
+      </c>
+      <c r="D48">
+        <v>-489.53300000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>3.0094000000000003E-2</v>
+      </c>
+      <c r="B49">
+        <v>481.05599999999998</v>
+      </c>
+      <c r="C49">
+        <v>-2.2609999999999998E-2</v>
+      </c>
+      <c r="D49">
+        <v>-493.57900000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>3.3104000000000001E-2</v>
+      </c>
+      <c r="B50">
+        <v>482.66399999999999</v>
+      </c>
+      <c r="C50">
+        <v>-2.4870999999999997E-2</v>
+      </c>
+      <c r="D50">
+        <v>-497.52100000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>3.6414000000000002E-2</v>
+      </c>
+      <c r="B51">
+        <v>485.85700000000003</v>
+      </c>
+      <c r="C51">
+        <v>-2.7358E-2</v>
+      </c>
+      <c r="D51">
+        <v>-501.22500000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>3.7142000000000001E-2</v>
+      </c>
+      <c r="B52">
+        <v>486.97399999999999</v>
+      </c>
+      <c r="C52">
+        <v>-3.0094000000000003E-2</v>
+      </c>
+      <c r="D52">
+        <v>-504.53800000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>3.7259E-2</v>
+      </c>
+      <c r="B53">
+        <v>487.12</v>
+      </c>
+      <c r="C53">
+        <v>-3.3104000000000001E-2</v>
+      </c>
+      <c r="D53">
+        <v>-506.69099999999997</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>3.7351999999999996E-2</v>
+      </c>
+      <c r="B54">
+        <v>487.27699999999999</v>
+      </c>
+      <c r="C54">
+        <v>-3.6414000000000002E-2</v>
+      </c>
+      <c r="D54">
+        <v>-505.22199999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>3.7427000000000002E-2</v>
+      </c>
+      <c r="B55">
+        <v>487.40300000000002</v>
+      </c>
+      <c r="C55">
+        <v>-4.0055999999999994E-2</v>
+      </c>
+      <c r="D55">
+        <v>-503.92899999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>3.7485999999999998E-2</v>
+      </c>
+      <c r="B56">
+        <v>487.49200000000002</v>
+      </c>
+      <c r="C56">
+        <v>-4.4061000000000003E-2</v>
+      </c>
+      <c r="D56">
+        <v>-504.69499999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>3.7725000000000002E-2</v>
+      </c>
+      <c r="B57">
+        <v>487.84300000000002</v>
+      </c>
+      <c r="C57">
+        <v>-4.8466999999999996E-2</v>
+      </c>
+      <c r="D57">
+        <v>-507.29399999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>4.0055999999999994E-2</v>
+      </c>
+      <c r="B58">
+        <v>491.56200000000001</v>
+      </c>
+      <c r="C58">
+        <v>-5.3314E-2</v>
+      </c>
+      <c r="D58">
+        <v>-510.75099999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>4.4061000000000003E-2</v>
+      </c>
+      <c r="B59">
+        <v>498.68200000000002</v>
+      </c>
+      <c r="C59">
+        <v>-5.8645000000000003E-2</v>
+      </c>
+      <c r="D59">
+        <v>-511.303</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>4.8466999999999996E-2</v>
+      </c>
+      <c r="B60">
+        <v>505.524</v>
+      </c>
+      <c r="C60">
+        <v>-6.4510000000000012E-2</v>
+      </c>
+      <c r="D60">
+        <v>-510.40499999999997</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>5.3314E-2</v>
+      </c>
+      <c r="B61">
+        <v>511.464</v>
+      </c>
+      <c r="C61">
+        <v>-7.0960999999999996E-2</v>
+      </c>
+      <c r="D61">
+        <v>-510.68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>5.8645000000000003E-2</v>
+      </c>
+      <c r="B62">
+        <v>516.15200000000004</v>
+      </c>
+      <c r="C62">
+        <v>-7.8057000000000001E-2</v>
+      </c>
+      <c r="D62">
+        <v>-512.13400000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>6.4510000000000012E-2</v>
+      </c>
+      <c r="B63">
+        <v>519.15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>7.0960999999999996E-2</v>
+      </c>
+      <c r="B64">
+        <v>520.596</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>7.8057000000000001E-2</v>
+      </c>
+      <c r="B65">
+        <v>521.44899999999996</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>8.5862999999999995E-2</v>
+      </c>
+      <c r="B66">
+        <v>522.23900000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>9.4448999999999991E-2</v>
+      </c>
+      <c r="B67">
+        <v>524.22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>0.103894</v>
+      </c>
+      <c r="B68">
+        <v>528.12400000000002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>0.114283</v>
+      </c>
+      <c r="B69">
+        <v>529.25699999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45EEDC87-E53A-4701-A823-B22DF4B10955}">
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -2326,16 +5003,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2354,810 +5031,4496 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>5.1E-5</v>
+        <v>6.7000000000000002E-5</v>
       </c>
       <c r="B5">
-        <v>22.33</v>
+        <v>10.74</v>
       </c>
       <c r="C5">
-        <v>-5.1E-5</v>
+        <v>-6.7000000000000002E-5</v>
       </c>
       <c r="D5">
-        <v>-22.324999999999999</v>
+        <v>-10.737</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>1.1300000000000001E-4</v>
+        <v>1.47E-4</v>
       </c>
       <c r="B6">
-        <v>49.125</v>
+        <v>23.628</v>
       </c>
       <c r="C6">
-        <v>-3.59E-4</v>
+        <v>-1.47E-4</v>
       </c>
       <c r="D6">
-        <v>-156.22900000000001</v>
+        <v>-23.622</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>1.6200000000000001E-4</v>
+        <v>2.1100000000000001E-4</v>
       </c>
       <c r="B7">
-        <v>70.56</v>
+        <v>33.938000000000002</v>
       </c>
       <c r="C7">
-        <v>-3.7100000000000002E-4</v>
+        <v>-2.1100000000000001E-4</v>
       </c>
       <c r="D7">
-        <v>-161.58099999999999</v>
+        <v>-33.929000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>2.0100000000000001E-4</v>
+        <v>2.6200000000000003E-4</v>
       </c>
       <c r="B8">
-        <v>87.707999999999998</v>
+        <v>42.186</v>
       </c>
       <c r="C8">
-        <v>-3.8099999999999999E-4</v>
+        <v>-2.6200000000000003E-4</v>
       </c>
       <c r="D8">
-        <v>-165.863</v>
+        <v>-42.174999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>2.3300000000000003E-4</v>
+        <v>3.0299999999999999E-4</v>
       </c>
       <c r="B9">
-        <v>101.426</v>
+        <v>48.783999999999999</v>
       </c>
       <c r="C9">
-        <v>-3.8900000000000002E-4</v>
+        <v>-3.0299999999999999E-4</v>
       </c>
       <c r="D9">
-        <v>-169.28800000000001</v>
+        <v>-48.771999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>2.5799999999999998E-4</v>
+        <v>3.3600000000000004E-4</v>
       </c>
       <c r="B10">
-        <v>112.399</v>
+        <v>54.063000000000002</v>
       </c>
       <c r="C10">
-        <v>-3.9500000000000001E-4</v>
+        <v>-3.3600000000000004E-4</v>
       </c>
       <c r="D10">
-        <v>-172.02799999999999</v>
+        <v>-54.05</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>2.7800000000000004E-4</v>
+        <v>3.4100000000000005E-4</v>
       </c>
       <c r="B11">
-        <v>121.178</v>
+        <v>54.908000000000001</v>
       </c>
       <c r="C11">
-        <v>-4.0000000000000002E-4</v>
+        <v>-3.6199999999999996E-4</v>
       </c>
       <c r="D11">
-        <v>-174.21899999999999</v>
+        <v>-58.271000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>2.8199999999999997E-4</v>
+        <v>3.4499999999999998E-4</v>
       </c>
       <c r="B12">
-        <v>122.58199999999999</v>
+        <v>55.584000000000003</v>
       </c>
       <c r="C12">
-        <v>-4.0400000000000001E-4</v>
+        <v>-3.8299999999999999E-4</v>
       </c>
       <c r="D12">
-        <v>-175.97300000000001</v>
+        <v>-61.649000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>2.8399999999999996E-4</v>
+        <v>3.48E-4</v>
       </c>
       <c r="B13">
-        <v>123.706</v>
+        <v>56.124000000000002</v>
       </c>
       <c r="C13">
-        <v>-4.08E-4</v>
+        <v>-4.0000000000000002E-4</v>
       </c>
       <c r="D13">
-        <v>-177.375</v>
+        <v>-64.350999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>2.8599999999999996E-4</v>
+        <v>3.5099999999999997E-4</v>
       </c>
       <c r="B14">
-        <v>109.47799999999999</v>
+        <v>56.555999999999997</v>
       </c>
       <c r="C14">
-        <v>-4.0999999999999999E-4</v>
+        <v>-4.1299999999999996E-4</v>
       </c>
       <c r="D14">
-        <v>-178.49700000000001</v>
+        <v>-66.513000000000005</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>2.9399999999999999E-4</v>
+        <v>3.5299999999999996E-4</v>
       </c>
       <c r="B15">
-        <v>105.384</v>
+        <v>56.902999999999999</v>
       </c>
       <c r="C15">
-        <v>-4.1199999999999999E-4</v>
+        <v>-4.2400000000000001E-4</v>
       </c>
       <c r="D15">
-        <v>-179.39500000000001</v>
+        <v>-68.242000000000004</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>3.59E-4</v>
+        <v>3.5499999999999996E-4</v>
       </c>
       <c r="B16">
-        <v>113.057</v>
+        <v>57.179000000000002</v>
       </c>
       <c r="C16">
-        <v>-4.2099999999999999E-4</v>
+        <v>-4.3199999999999998E-4</v>
       </c>
       <c r="D16">
-        <v>-140.54</v>
+        <v>-69.625</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>6.6700000000000006E-4</v>
+        <v>3.6199999999999996E-4</v>
       </c>
       <c r="B17">
-        <v>133.417</v>
+        <v>57.637999999999998</v>
       </c>
       <c r="C17">
-        <v>-6.6700000000000006E-4</v>
+        <v>-4.3899999999999999E-4</v>
       </c>
       <c r="D17">
-        <v>-161.30500000000001</v>
+        <v>-70.731999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>9.7399999999999993E-4</v>
+        <v>4.6700000000000002E-4</v>
       </c>
       <c r="B18">
-        <v>147.267</v>
+        <v>61.359000000000002</v>
       </c>
       <c r="C18">
-        <v>-9.7399999999999993E-4</v>
+        <v>-4.4500000000000003E-4</v>
       </c>
       <c r="D18">
-        <v>-178.511</v>
+        <v>-71.617000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>1.2819999999999999E-3</v>
+        <v>8.6700000000000004E-4</v>
       </c>
       <c r="B19">
-        <v>160.37</v>
+        <v>85.647999999999996</v>
       </c>
       <c r="C19">
-        <v>-1.2819999999999999E-3</v>
+        <v>-4.4900000000000002E-4</v>
       </c>
       <c r="D19">
-        <v>-193.47200000000001</v>
+        <v>-72.325999999999993</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>1.5900000000000001E-3</v>
+        <v>1.2669999999999999E-3</v>
       </c>
       <c r="B20">
-        <v>173.59800000000001</v>
+        <v>107.35599999999999</v>
       </c>
       <c r="C20">
-        <v>-1.5900000000000001E-3</v>
+        <v>-4.5300000000000001E-4</v>
       </c>
       <c r="D20">
-        <v>-208.00800000000001</v>
+        <v>-72.891999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>1.897E-3</v>
+        <v>1.6670000000000001E-3</v>
       </c>
       <c r="B21">
-        <v>187.12899999999999</v>
+        <v>128.791</v>
       </c>
       <c r="C21">
-        <v>-1.897E-3</v>
+        <v>-4.55E-4</v>
       </c>
       <c r="D21">
-        <v>-222.482</v>
+        <v>-73.346000000000004</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>2.2049999999999999E-3</v>
+        <v>2.0670000000000003E-3</v>
       </c>
       <c r="B22">
-        <v>200.97399999999999</v>
+        <v>150.25700000000001</v>
       </c>
       <c r="C22">
-        <v>-2.2049999999999999E-3</v>
+        <v>-4.5800000000000002E-4</v>
       </c>
       <c r="D22">
-        <v>-237.21100000000001</v>
+        <v>-73.707999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>2.513E-3</v>
+        <v>2.467E-3</v>
       </c>
       <c r="B23">
-        <v>215.101</v>
+        <v>171.81399999999999</v>
       </c>
       <c r="C23">
-        <v>-2.513E-3</v>
+        <v>-4.6700000000000002E-4</v>
       </c>
       <c r="D23">
-        <v>-252.095</v>
+        <v>-69.585999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>2.8210000000000002E-3</v>
+        <v>2.8670000000000002E-3</v>
       </c>
       <c r="B24">
-        <v>229.45</v>
+        <v>193.46100000000001</v>
       </c>
       <c r="C24">
-        <v>-2.8210000000000002E-3</v>
+        <v>-8.6700000000000004E-4</v>
       </c>
       <c r="D24">
-        <v>-267.21699999999998</v>
+        <v>-91.153000000000006</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>3.1280000000000001E-3</v>
+        <v>3.2669999999999999E-3</v>
       </c>
       <c r="B25">
-        <v>243.98099999999999</v>
+        <v>215.16900000000001</v>
       </c>
       <c r="C25">
-        <v>-3.1280000000000001E-3</v>
+        <v>-1.2669999999999999E-3</v>
       </c>
       <c r="D25">
-        <v>-282.54000000000002</v>
+        <v>-112.157</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>3.441E-3</v>
+        <v>3.6669999999999997E-3</v>
       </c>
       <c r="B26">
-        <v>257.75200000000001</v>
+        <v>236.94499999999999</v>
       </c>
       <c r="C26">
-        <v>-3.441E-3</v>
+        <v>-1.6670000000000001E-3</v>
       </c>
       <c r="D26">
-        <v>-297.738</v>
+        <v>-132.59399999999999</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>3.7850000000000002E-3</v>
+        <v>4.0670000000000003E-3</v>
       </c>
       <c r="B27">
-        <v>269.91000000000003</v>
+        <v>258.77</v>
       </c>
       <c r="C27">
-        <v>-3.7850000000000002E-3</v>
+        <v>-2.0670000000000003E-3</v>
       </c>
       <c r="D27">
-        <v>-313.09199999999998</v>
+        <v>-152.96899999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>4.1639999999999993E-3</v>
+        <v>4.4729999999999995E-3</v>
       </c>
       <c r="B28">
-        <v>271.22399999999999</v>
+        <v>281.00099999999998</v>
       </c>
       <c r="C28">
-        <v>-4.1639999999999993E-3</v>
+        <v>-2.467E-3</v>
       </c>
       <c r="D28">
-        <v>-314.82900000000001</v>
+        <v>-173.37100000000001</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>4.5799999999999999E-3</v>
+        <v>4.921E-3</v>
       </c>
       <c r="B29">
-        <v>272.81799999999998</v>
+        <v>305.49299999999999</v>
       </c>
       <c r="C29">
-        <v>-4.5799999999999999E-3</v>
+        <v>-2.8670000000000002E-3</v>
       </c>
       <c r="D29">
-        <v>-316.11799999999999</v>
+        <v>-193.84399999999999</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>5.0379999999999999E-3</v>
+        <v>5.4130000000000003E-3</v>
       </c>
       <c r="B30">
-        <v>275.45600000000002</v>
+        <v>332.464</v>
       </c>
       <c r="C30">
-        <v>-5.0379999999999999E-3</v>
+        <v>-3.2669999999999999E-3</v>
       </c>
       <c r="D30">
-        <v>-317.87799999999999</v>
+        <v>-214.38499999999999</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>5.5420000000000001E-3</v>
+        <v>5.9540000000000001E-3</v>
       </c>
       <c r="B31">
-        <v>278.69099999999997</v>
+        <v>362.15800000000002</v>
       </c>
       <c r="C31">
-        <v>-5.5420000000000001E-3</v>
+        <v>-3.6669999999999997E-3</v>
       </c>
       <c r="D31">
-        <v>-320.39499999999998</v>
+        <v>-234.97800000000001</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>6.0959999999999999E-3</v>
+        <v>6.5490000000000001E-3</v>
       </c>
       <c r="B32">
-        <v>282.55799999999999</v>
+        <v>394.834</v>
       </c>
       <c r="C32">
-        <v>-6.0959999999999999E-3</v>
+        <v>-4.0670000000000003E-3</v>
       </c>
       <c r="D32">
-        <v>-323.74299999999999</v>
+        <v>-255.614</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>6.7060000000000002E-3</v>
+        <v>7.2039999999999995E-3</v>
       </c>
       <c r="B33">
-        <v>286.89100000000002</v>
+        <v>421.04500000000002</v>
       </c>
       <c r="C33">
-        <v>-6.7060000000000002E-3</v>
+        <v>-4.4729999999999995E-3</v>
       </c>
       <c r="D33">
-        <v>-327.28800000000001</v>
+        <v>-276.62299999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>7.3760000000000006E-3</v>
+        <v>7.9249999999999998E-3</v>
       </c>
       <c r="B34">
-        <v>291.66000000000003</v>
+        <v>422.45100000000002</v>
       </c>
       <c r="C34">
-        <v>-7.3760000000000006E-3</v>
+        <v>-4.921E-3</v>
       </c>
       <c r="D34">
-        <v>-331.05</v>
+        <v>-299.75599999999997</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>8.1140000000000014E-3</v>
+        <v>8.7170000000000008E-3</v>
       </c>
       <c r="B35">
-        <v>296.85300000000001</v>
+        <v>424.95</v>
       </c>
       <c r="C35">
-        <v>-8.1140000000000014E-3</v>
+        <v>-5.4130000000000003E-3</v>
       </c>
       <c r="D35">
-        <v>-335.053</v>
+        <v>-325.209</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>8.9250000000000006E-3</v>
+        <v>9.5890000000000003E-3</v>
       </c>
       <c r="B36">
-        <v>302.53500000000003</v>
+        <v>427.79</v>
       </c>
       <c r="C36">
-        <v>-8.9250000000000006E-3</v>
+        <v>-5.9540000000000001E-3</v>
       </c>
       <c r="D36">
-        <v>-339.29300000000001</v>
+        <v>-353.19200000000001</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>9.8180000000000003E-3</v>
+        <v>1.0548E-2</v>
       </c>
       <c r="B37">
-        <v>308.40300000000002</v>
+        <v>430.89299999999997</v>
       </c>
       <c r="C37">
-        <v>-9.8180000000000003E-3</v>
+        <v>-6.5490000000000001E-3</v>
       </c>
       <c r="D37">
-        <v>-343.79700000000003</v>
+        <v>-383.923</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>1.0799E-2</v>
+        <v>1.1603E-2</v>
       </c>
       <c r="B38">
-        <v>314.17500000000001</v>
+        <v>434.108</v>
       </c>
       <c r="C38">
-        <v>-1.0799E-2</v>
+        <v>-7.2039999999999995E-3</v>
       </c>
       <c r="D38">
-        <v>-348.57900000000001</v>
+        <v>-417.62599999999998</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>1.1878999999999999E-2</v>
+        <v>1.2763E-2</v>
       </c>
       <c r="B39">
-        <v>315.59800000000001</v>
+        <v>437.64</v>
       </c>
       <c r="C39">
-        <v>-1.1878999999999999E-2</v>
+        <v>-7.9249999999999998E-3</v>
       </c>
       <c r="D39">
-        <v>-353.61900000000003</v>
+        <v>-443.66199999999998</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>1.3067E-2</v>
+        <v>1.4038999999999999E-2</v>
       </c>
       <c r="B40">
-        <v>315.77100000000002</v>
+        <v>441.79300000000001</v>
       </c>
       <c r="C40">
-        <v>-1.3067E-2</v>
+        <v>-8.7170000000000008E-3</v>
       </c>
       <c r="D40">
-        <v>-358.911</v>
+        <v>-445.54700000000003</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>1.4374000000000001E-2</v>
+        <v>1.5443E-2</v>
       </c>
       <c r="B41">
-        <v>315.60000000000002</v>
+        <v>446.53800000000001</v>
       </c>
       <c r="C41">
-        <v>-1.4374000000000001E-2</v>
+        <v>-9.5890000000000003E-3</v>
       </c>
       <c r="D41">
-        <v>-364.488</v>
+        <v>-448.51299999999998</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>1.5810999999999999E-2</v>
+        <v>1.6986999999999999E-2</v>
       </c>
       <c r="B42">
-        <v>315.34699999999998</v>
+        <v>451.68099999999998</v>
       </c>
       <c r="C42">
-        <v>-1.5810999999999999E-2</v>
+        <v>-1.0548E-2</v>
       </c>
       <c r="D42">
-        <v>-370.45</v>
+        <v>-451.791</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>1.7393000000000002E-2</v>
+        <v>1.8686000000000001E-2</v>
       </c>
       <c r="B43">
-        <v>314.94299999999998</v>
+        <v>457.11900000000003</v>
       </c>
       <c r="C43">
-        <v>-1.7393000000000002E-2</v>
+        <v>-1.1603E-2</v>
       </c>
       <c r="D43">
-        <v>-376.63499999999999</v>
+        <v>-455.10199999999998</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>1.9132000000000003E-2</v>
+        <v>2.0555E-2</v>
       </c>
       <c r="B44">
-        <v>314.577</v>
+        <v>462.33600000000001</v>
       </c>
       <c r="C44">
-        <v>-1.9132000000000003E-2</v>
+        <v>-1.2763E-2</v>
       </c>
       <c r="D44">
-        <v>-381.553</v>
+        <v>-458.495</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>2.1045000000000001E-2</v>
+        <v>2.2609999999999998E-2</v>
       </c>
       <c r="B45">
-        <v>314.21199999999999</v>
+        <v>465.51799999999997</v>
       </c>
       <c r="C45">
-        <v>-2.1045000000000001E-2</v>
+        <v>-1.4038999999999999E-2</v>
       </c>
       <c r="D45">
-        <v>-380.74400000000003</v>
+        <v>-461.97</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>2.3148999999999999E-2</v>
+        <v>2.4870999999999997E-2</v>
       </c>
       <c r="B46">
-        <v>313.99200000000002</v>
+        <v>466.935</v>
       </c>
       <c r="C46">
-        <v>-2.3148999999999999E-2</v>
+        <v>-1.5443E-2</v>
       </c>
       <c r="D46">
-        <v>-379.625</v>
+        <v>-465.54700000000003</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>2.5463999999999997E-2</v>
+        <v>2.7358E-2</v>
       </c>
       <c r="B47">
-        <v>313.83100000000002</v>
+        <v>468.26499999999999</v>
       </c>
       <c r="C47">
-        <v>-2.3611999999999998E-2</v>
+        <v>-1.6986999999999999E-2</v>
       </c>
       <c r="D47">
-        <v>-379.37400000000002</v>
+        <v>-469.21199999999999</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>2.8010999999999998E-2</v>
+        <v>3.0094000000000003E-2</v>
       </c>
       <c r="B48">
-        <v>316.75799999999998</v>
+        <v>469.53</v>
       </c>
       <c r="C48">
-        <v>-2.3983000000000001E-2</v>
+        <v>-1.8686000000000001E-2</v>
       </c>
       <c r="D48">
-        <v>-379.12700000000001</v>
+        <v>-472.94099999999997</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>3.0812000000000003E-2</v>
+        <v>3.0696000000000001E-2</v>
       </c>
       <c r="B49">
-        <v>320.29199999999997</v>
+        <v>469.78300000000002</v>
       </c>
       <c r="C49">
-        <v>-2.4278999999999998E-2</v>
+        <v>-2.0555E-2</v>
       </c>
       <c r="D49">
-        <v>-378.93700000000001</v>
+        <v>-476.85300000000001</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>3.3893E-2</v>
+        <v>3.0793000000000001E-2</v>
       </c>
       <c r="B50">
-        <v>324.19</v>
+        <v>469.82</v>
       </c>
       <c r="C50">
-        <v>-2.4516E-2</v>
+        <v>-2.0636999999999999E-2</v>
       </c>
       <c r="D50">
-        <v>-378.79199999999997</v>
+        <v>-476.99400000000003</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>3.7283000000000004E-2</v>
+        <v>3.0870000000000002E-2</v>
       </c>
       <c r="B51">
-        <v>328.601</v>
+        <v>469.84800000000001</v>
       </c>
       <c r="C51">
-        <v>-2.4705999999999999E-2</v>
+        <v>-2.0702999999999999E-2</v>
       </c>
       <c r="D51">
-        <v>-378.62299999999999</v>
+        <v>-477.13499999999999</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>4.1011000000000006E-2</v>
+        <v>3.0931E-2</v>
       </c>
       <c r="B52">
-        <v>333.39499999999998</v>
+        <v>469.87700000000001</v>
       </c>
       <c r="C52">
-        <v>-2.4858000000000002E-2</v>
+        <v>-2.0754999999999999E-2</v>
       </c>
       <c r="D52">
-        <v>-378.625</v>
+        <v>-477.25400000000002</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>4.5111999999999999E-2</v>
+        <v>3.0981000000000002E-2</v>
       </c>
       <c r="B53">
-        <v>338.52300000000002</v>
+        <v>469.899</v>
       </c>
       <c r="C53">
-        <v>-2.4978999999999998E-2</v>
+        <v>-2.0797999999999997E-2</v>
       </c>
       <c r="D53">
-        <v>-378.41800000000001</v>
+        <v>-477.334</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>4.9623E-2</v>
+        <v>3.1019999999999999E-2</v>
       </c>
       <c r="B54">
-        <v>343.791</v>
+        <v>469.91699999999997</v>
       </c>
       <c r="C54">
-        <v>-2.5076000000000001E-2</v>
+        <v>-2.0966000000000002E-2</v>
       </c>
       <c r="D54">
-        <v>-378.464</v>
+        <v>-477.65699999999998</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>5.0615E-2</v>
+        <v>3.1052E-2</v>
       </c>
       <c r="B55">
-        <v>344.92899999999997</v>
+        <v>469.923</v>
       </c>
       <c r="C55">
-        <v>-2.5463999999999997E-2</v>
+        <v>-2.2609999999999998E-2</v>
       </c>
       <c r="D55">
-        <v>-378.26799999999997</v>
+        <v>-480.78300000000002</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>5.1707000000000003E-2</v>
+        <v>3.1178000000000001E-2</v>
       </c>
       <c r="B56">
-        <v>346.05599999999998</v>
+        <v>469.97300000000001</v>
       </c>
       <c r="C56">
-        <v>-2.8010999999999998E-2</v>
+        <v>-2.4870999999999997E-2</v>
       </c>
       <c r="D56">
-        <v>-377.94799999999998</v>
+        <v>-484.58800000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>3.3104000000000001E-2</v>
+      </c>
+      <c r="B57">
+        <v>470.69600000000003</v>
+      </c>
+      <c r="C57">
+        <v>-2.7358E-2</v>
+      </c>
+      <c r="D57">
+        <v>-487.93200000000002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>3.6414000000000002E-2</v>
+      </c>
+      <c r="B58">
+        <v>471.99599999999998</v>
+      </c>
+      <c r="C58">
+        <v>-3.0094000000000003E-2</v>
+      </c>
+      <c r="D58">
+        <v>-490.14800000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>4.0055999999999994E-2</v>
+      </c>
+      <c r="B59">
+        <v>475.65499999999997</v>
+      </c>
+      <c r="C59">
+        <v>-3.3104000000000001E-2</v>
+      </c>
+      <c r="D59">
+        <v>-489.93400000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>4.4061000000000003E-2</v>
+      </c>
+      <c r="B60">
+        <v>480.54199999999997</v>
+      </c>
+      <c r="C60">
+        <v>-3.6414000000000002E-2</v>
+      </c>
+      <c r="D60">
+        <v>-488.101</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>4.8466999999999996E-2</v>
+      </c>
+      <c r="B61">
+        <v>484.77600000000001</v>
+      </c>
+      <c r="C61">
+        <v>-4.0055999999999994E-2</v>
+      </c>
+      <c r="D61">
+        <v>-487.19200000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>5.3314E-2</v>
+      </c>
+      <c r="B62">
+        <v>487.976</v>
+      </c>
+      <c r="C62">
+        <v>-4.4061000000000003E-2</v>
+      </c>
+      <c r="D62">
+        <v>-488.13900000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>5.8645000000000003E-2</v>
+      </c>
+      <c r="B63">
+        <v>490.32299999999998</v>
+      </c>
+      <c r="C63">
+        <v>-4.8466999999999996E-2</v>
+      </c>
+      <c r="D63">
+        <v>-490.82900000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>6.4510000000000012E-2</v>
+      </c>
+      <c r="B64">
+        <v>492.24099999999999</v>
+      </c>
+      <c r="C64">
+        <v>-5.3314E-2</v>
+      </c>
+      <c r="D64">
+        <v>-494.19799999999998</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>7.0960999999999996E-2</v>
+      </c>
+      <c r="B65">
+        <v>494.15300000000002</v>
+      </c>
+      <c r="C65">
+        <v>-5.8645000000000003E-2</v>
+      </c>
+      <c r="D65">
+        <v>-497.20100000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>7.8057000000000001E-2</v>
+      </c>
+      <c r="B66">
+        <v>496.91</v>
+      </c>
+      <c r="C66">
+        <v>-6.4510000000000012E-2</v>
+      </c>
+      <c r="D66">
+        <v>-496.37900000000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>8.5862999999999995E-2</v>
+      </c>
+      <c r="B67">
+        <v>501.12200000000001</v>
+      </c>
+      <c r="C67">
+        <v>-7.0960999999999996E-2</v>
+      </c>
+      <c r="D67">
+        <v>-496.649</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>9.4448999999999991E-2</v>
+      </c>
+      <c r="B68">
+        <v>503.435</v>
+      </c>
+      <c r="C68">
+        <v>-7.8057000000000001E-2</v>
+      </c>
+      <c r="D68">
+        <v>-498.04300000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>0.103894</v>
+      </c>
+      <c r="B69">
+        <v>503.67099999999999</v>
+      </c>
+      <c r="C69">
+        <v>-8.5862999999999995E-2</v>
+      </c>
+      <c r="D69">
+        <v>-500.67099999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694005ED-B4C9-43F6-85C0-2FBBFF9EE24B}">
+  <dimension ref="A1:D76"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>6.7000000000000002E-5</v>
+      </c>
+      <c r="B5">
+        <v>15.474</v>
+      </c>
+      <c r="C5">
+        <v>-6.7000000000000002E-5</v>
+      </c>
+      <c r="D5">
+        <v>-15.465</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1.47E-4</v>
+      </c>
+      <c r="B6">
+        <v>34.042999999999999</v>
+      </c>
+      <c r="C6">
+        <v>-4.6700000000000002E-4</v>
+      </c>
+      <c r="D6">
+        <v>-108.255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2.1100000000000001E-4</v>
+      </c>
+      <c r="B7">
+        <v>48.898000000000003</v>
+      </c>
+      <c r="C7">
+        <v>-5.4700000000000007E-4</v>
+      </c>
+      <c r="D7">
+        <v>-126.81100000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2.6200000000000003E-4</v>
+      </c>
+      <c r="B8">
+        <v>60.781999999999996</v>
+      </c>
+      <c r="C8">
+        <v>-6.11E-4</v>
+      </c>
+      <c r="D8">
+        <v>-141.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2.7E-4</v>
+      </c>
+      <c r="B9">
+        <v>62.683</v>
+      </c>
+      <c r="C9">
+        <v>-6.2100000000000002E-4</v>
+      </c>
+      <c r="D9">
+        <v>-144.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2.7700000000000001E-4</v>
+      </c>
+      <c r="B10">
+        <v>64.203999999999994</v>
+      </c>
+      <c r="C10">
+        <v>-6.29E-4</v>
+      </c>
+      <c r="D10">
+        <v>-132.279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2.8199999999999997E-4</v>
+      </c>
+      <c r="B11">
+        <v>65.421000000000006</v>
+      </c>
+      <c r="C11">
+        <v>-6.6200000000000005E-4</v>
+      </c>
+      <c r="D11">
+        <v>-131.09200000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2.8599999999999996E-4</v>
+      </c>
+      <c r="B12">
+        <v>66.394999999999996</v>
+      </c>
+      <c r="C12">
+        <v>-8.6700000000000004E-4</v>
+      </c>
+      <c r="D12">
+        <v>-143.82499999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2.8899999999999998E-4</v>
+      </c>
+      <c r="B13">
+        <v>67.174000000000007</v>
+      </c>
+      <c r="C13">
+        <v>-1.2669999999999999E-3</v>
+      </c>
+      <c r="D13">
+        <v>-166.19300000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2.92E-4</v>
+      </c>
+      <c r="B14">
+        <v>66.864000000000004</v>
+      </c>
+      <c r="C14">
+        <v>-1.6670000000000001E-3</v>
+      </c>
+      <c r="D14">
+        <v>-187.11500000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>3.0299999999999999E-4</v>
+      </c>
+      <c r="B15">
+        <v>64.840999999999994</v>
+      </c>
+      <c r="C15">
+        <v>-2.0670000000000003E-3</v>
+      </c>
+      <c r="D15">
+        <v>-207.863</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>4.6700000000000002E-4</v>
+      </c>
+      <c r="B16">
+        <v>76.174999999999997</v>
+      </c>
+      <c r="C16">
+        <v>-2.467E-3</v>
+      </c>
+      <c r="D16">
+        <v>-228.68899999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>8.6700000000000004E-4</v>
+      </c>
+      <c r="B17">
+        <v>102.233</v>
+      </c>
+      <c r="C17">
+        <v>-2.8670000000000002E-3</v>
+      </c>
+      <c r="D17">
+        <v>-249.69900000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>1.2669999999999999E-3</v>
+      </c>
+      <c r="B18">
+        <v>126.96299999999999</v>
+      </c>
+      <c r="C18">
+        <v>-3.2669999999999999E-3</v>
+      </c>
+      <c r="D18">
+        <v>-270.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1.6670000000000001E-3</v>
+      </c>
+      <c r="B19">
+        <v>151.71600000000001</v>
+      </c>
+      <c r="C19">
+        <v>-3.6669999999999997E-3</v>
+      </c>
+      <c r="D19">
+        <v>-292.20800000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2.0670000000000003E-3</v>
+      </c>
+      <c r="B20">
+        <v>176.63200000000001</v>
+      </c>
+      <c r="C20">
+        <v>-4.0670000000000003E-3</v>
+      </c>
+      <c r="D20">
+        <v>-313.65800000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2.467E-3</v>
+      </c>
+      <c r="B21">
+        <v>201.702</v>
+      </c>
+      <c r="C21">
+        <v>-4.4729999999999995E-3</v>
+      </c>
+      <c r="D21">
+        <v>-335.56200000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2.8670000000000002E-3</v>
+      </c>
+      <c r="B22">
+        <v>226.88800000000001</v>
+      </c>
+      <c r="C22">
+        <v>-4.921E-3</v>
+      </c>
+      <c r="D22">
+        <v>-359.74200000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>3.2669999999999999E-3</v>
+      </c>
+      <c r="B23">
+        <v>252.20400000000001</v>
+      </c>
+      <c r="C23">
+        <v>-5.4130000000000003E-3</v>
+      </c>
+      <c r="D23">
+        <v>-386.404</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>3.6669999999999997E-3</v>
+      </c>
+      <c r="B24">
+        <v>277.608</v>
+      </c>
+      <c r="C24">
+        <v>-5.9540000000000001E-3</v>
+      </c>
+      <c r="D24">
+        <v>-415.77100000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>4.0670000000000003E-3</v>
+      </c>
+      <c r="B25">
+        <v>303.05200000000002</v>
+      </c>
+      <c r="C25">
+        <v>-6.5490000000000001E-3</v>
+      </c>
+      <c r="D25">
+        <v>-448.06700000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>4.4729999999999995E-3</v>
+      </c>
+      <c r="B26">
+        <v>328.99400000000003</v>
+      </c>
+      <c r="C26">
+        <v>-7.2039999999999995E-3</v>
+      </c>
+      <c r="D26">
+        <v>-483.19400000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>4.921E-3</v>
+      </c>
+      <c r="B27">
+        <v>357.57900000000001</v>
+      </c>
+      <c r="C27">
+        <v>-7.9249999999999998E-3</v>
+      </c>
+      <c r="D27">
+        <v>-489.69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>5.4130000000000003E-3</v>
+      </c>
+      <c r="B28">
+        <v>389.05599999999998</v>
+      </c>
+      <c r="C28">
+        <v>-8.7170000000000008E-3</v>
+      </c>
+      <c r="D28">
+        <v>-493.39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>5.9540000000000001E-3</v>
+      </c>
+      <c r="B29">
+        <v>423.69900000000001</v>
+      </c>
+      <c r="C29">
+        <v>-9.5890000000000003E-3</v>
+      </c>
+      <c r="D29">
+        <v>-497.69099999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>6.5490000000000001E-3</v>
+      </c>
+      <c r="B30">
+        <v>447.55900000000003</v>
+      </c>
+      <c r="C30">
+        <v>-1.0548E-2</v>
+      </c>
+      <c r="D30">
+        <v>-501.81799999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>7.2039999999999995E-3</v>
+      </c>
+      <c r="B31">
+        <v>452.77600000000001</v>
+      </c>
+      <c r="C31">
+        <v>-1.1603E-2</v>
+      </c>
+      <c r="D31">
+        <v>-506.02699999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>7.9249999999999998E-3</v>
+      </c>
+      <c r="B32">
+        <v>457.87</v>
+      </c>
+      <c r="C32">
+        <v>-1.2763E-2</v>
+      </c>
+      <c r="D32">
+        <v>-510.34399999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>8.7170000000000008E-3</v>
+      </c>
+      <c r="B33">
+        <v>462.43</v>
+      </c>
+      <c r="C33">
+        <v>-1.4038999999999999E-2</v>
+      </c>
+      <c r="D33">
+        <v>-514.774</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>9.5890000000000003E-3</v>
+      </c>
+      <c r="B34">
+        <v>467.08100000000002</v>
+      </c>
+      <c r="C34">
+        <v>-1.5443E-2</v>
+      </c>
+      <c r="D34">
+        <v>-519.31500000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1.0548E-2</v>
+      </c>
+      <c r="B35">
+        <v>471.88</v>
+      </c>
+      <c r="C35">
+        <v>-1.6986999999999999E-2</v>
+      </c>
+      <c r="D35">
+        <v>-523.89300000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1.1603E-2</v>
+      </c>
+      <c r="B36">
+        <v>476.92399999999998</v>
+      </c>
+      <c r="C36">
+        <v>-1.8686000000000001E-2</v>
+      </c>
+      <c r="D36">
+        <v>-528.79200000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1.2763E-2</v>
+      </c>
+      <c r="B37">
+        <v>481.78699999999998</v>
+      </c>
+      <c r="C37">
+        <v>-1.8761E-2</v>
+      </c>
+      <c r="D37">
+        <v>-528.98400000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1.4038999999999999E-2</v>
+      </c>
+      <c r="B38">
+        <v>485.125</v>
+      </c>
+      <c r="C38">
+        <v>-1.8821000000000001E-2</v>
+      </c>
+      <c r="D38">
+        <v>-529.14200000000005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1.5443E-2</v>
+      </c>
+      <c r="B39">
+        <v>487.17399999999998</v>
+      </c>
+      <c r="C39">
+        <v>-1.8869E-2</v>
+      </c>
+      <c r="D39">
+        <v>-529.29300000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1.6986999999999999E-2</v>
+      </c>
+      <c r="B40">
+        <v>489.18700000000001</v>
+      </c>
+      <c r="C40">
+        <v>-1.8907E-2</v>
+      </c>
+      <c r="D40">
+        <v>-529.39599999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1.8686000000000001E-2</v>
+      </c>
+      <c r="B41">
+        <v>491.45800000000003</v>
+      </c>
+      <c r="C41">
+        <v>-1.8937000000000002E-2</v>
+      </c>
+      <c r="D41">
+        <v>-529.48299999999995</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>2.0555E-2</v>
+      </c>
+      <c r="B42">
+        <v>493.55799999999999</v>
+      </c>
+      <c r="C42">
+        <v>-1.8962E-2</v>
+      </c>
+      <c r="D42">
+        <v>-529.55700000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>2.2609999999999998E-2</v>
+      </c>
+      <c r="B43">
+        <v>495.55599999999998</v>
+      </c>
+      <c r="C43">
+        <v>-1.8981999999999999E-2</v>
+      </c>
+      <c r="D43">
+        <v>-529.61099999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>2.4870999999999997E-2</v>
+      </c>
+      <c r="B44">
+        <v>497.71199999999999</v>
+      </c>
+      <c r="C44">
+        <v>-1.9059999999999997E-2</v>
+      </c>
+      <c r="D44">
+        <v>-529.94799999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>2.7358E-2</v>
+      </c>
+      <c r="B45">
+        <v>500.08199999999999</v>
+      </c>
+      <c r="C45">
+        <v>-2.0555E-2</v>
+      </c>
+      <c r="D45">
+        <v>-533.721</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>3.0094000000000003E-2</v>
+      </c>
+      <c r="B46">
+        <v>502.74599999999998</v>
+      </c>
+      <c r="C46">
+        <v>-2.2609999999999998E-2</v>
+      </c>
+      <c r="D46">
+        <v>-538.55700000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>3.3104000000000001E-2</v>
+      </c>
+      <c r="B47">
+        <v>505.60199999999998</v>
+      </c>
+      <c r="C47">
+        <v>-2.4870999999999997E-2</v>
+      </c>
+      <c r="D47">
+        <v>-543.25599999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>3.6414000000000002E-2</v>
+      </c>
+      <c r="B48">
+        <v>511.42899999999997</v>
+      </c>
+      <c r="C48">
+        <v>-2.7358E-2</v>
+      </c>
+      <c r="D48">
+        <v>-547.68299999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>4.0055999999999994E-2</v>
+      </c>
+      <c r="B49">
+        <v>519.84299999999996</v>
+      </c>
+      <c r="C49">
+        <v>-3.0094000000000003E-2</v>
+      </c>
+      <c r="D49">
+        <v>-551.803</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>4.4061000000000003E-2</v>
+      </c>
+      <c r="B50">
+        <v>529.68899999999996</v>
+      </c>
+      <c r="C50">
+        <v>-3.3104000000000001E-2</v>
+      </c>
+      <c r="D50">
+        <v>-555.49400000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>4.8466999999999996E-2</v>
+      </c>
+      <c r="B51">
+        <v>538.53899999999999</v>
+      </c>
+      <c r="C51">
+        <v>-3.6414000000000002E-2</v>
+      </c>
+      <c r="D51">
+        <v>-556.11300000000006</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>4.9436999999999995E-2</v>
+      </c>
+      <c r="B52">
+        <v>540.24800000000005</v>
+      </c>
+      <c r="C52">
+        <v>-4.0055999999999994E-2</v>
+      </c>
+      <c r="D52">
+        <v>-553.45600000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>5.0212000000000007E-2</v>
+      </c>
+      <c r="B53">
+        <v>541.58299999999997</v>
+      </c>
+      <c r="C53">
+        <v>-4.4061000000000003E-2</v>
+      </c>
+      <c r="D53">
+        <v>-553.76700000000005</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>5.0832000000000002E-2</v>
+      </c>
+      <c r="B54">
+        <v>542.63300000000004</v>
+      </c>
+      <c r="C54">
+        <v>-4.8466999999999996E-2</v>
+      </c>
+      <c r="D54">
+        <v>-556.13800000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>5.1329E-2</v>
+      </c>
+      <c r="B55">
+        <v>543.49900000000002</v>
+      </c>
+      <c r="C55">
+        <v>-5.3314E-2</v>
+      </c>
+      <c r="D55">
+        <v>-554.20299999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>5.1726000000000001E-2</v>
+      </c>
+      <c r="B56">
+        <v>544.15099999999995</v>
+      </c>
+      <c r="C56">
+        <v>-5.8645000000000003E-2</v>
+      </c>
+      <c r="D56">
+        <v>-552.03899999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>5.2042999999999999E-2</v>
+      </c>
+      <c r="B57">
+        <v>544.68200000000002</v>
+      </c>
+      <c r="C57">
+        <v>-6.4510000000000012E-2</v>
+      </c>
+      <c r="D57">
+        <v>-551.15899999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>5.2298000000000004E-2</v>
+      </c>
+      <c r="B58">
+        <v>545.10699999999997</v>
+      </c>
+      <c r="C58">
+        <v>-7.0960999999999996E-2</v>
+      </c>
+      <c r="D58">
+        <v>-551.56799999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>5.2500999999999999E-2</v>
+      </c>
+      <c r="B59">
+        <v>545.45600000000002</v>
+      </c>
+      <c r="C59">
+        <v>-7.8057000000000001E-2</v>
+      </c>
+      <c r="D59">
+        <v>-553.80100000000004</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>5.2662999999999995E-2</v>
+      </c>
+      <c r="B60">
+        <v>545.721</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>5.2793999999999994E-2</v>
+      </c>
+      <c r="B61">
+        <v>545.93799999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>5.2898000000000001E-2</v>
+      </c>
+      <c r="B62">
+        <v>546.154</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>5.2981E-2</v>
+      </c>
+      <c r="B63">
+        <v>546.25199999999995</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>5.3048000000000005E-2</v>
+      </c>
+      <c r="B64">
+        <v>546.351</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>5.3314E-2</v>
+      </c>
+      <c r="B65">
+        <v>546.803</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>5.8645000000000003E-2</v>
+      </c>
+      <c r="B66">
+        <v>555.39499999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>6.4510000000000012E-2</v>
+      </c>
+      <c r="B67">
+        <v>563.91399999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>7.0960999999999996E-2</v>
+      </c>
+      <c r="B68">
+        <v>572.21100000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>7.8057000000000001E-2</v>
+      </c>
+      <c r="B69">
+        <v>579.471</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>8.5862999999999995E-2</v>
+      </c>
+      <c r="B70">
+        <v>585.08000000000004</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>9.4448999999999991E-2</v>
+      </c>
+      <c r="B71">
+        <v>588.26599999999996</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>0.103894</v>
+      </c>
+      <c r="B72">
+        <v>588.78700000000003</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>0.114283</v>
+      </c>
+      <c r="B73">
+        <v>587.67200000000003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>0.12571199999999999</v>
+      </c>
+      <c r="B74">
+        <v>586.20100000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>0.13828299999999999</v>
+      </c>
+      <c r="B75">
+        <v>585.06100000000004</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>0.152111</v>
+      </c>
+      <c r="B76">
+        <v>585.40499999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7764A9F2-A9E3-43FB-BC73-6C4DCB0BAAD0}">
+  <dimension ref="A1:D63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>6.7000000000000002E-5</v>
+      </c>
+      <c r="B5">
+        <v>12.064</v>
+      </c>
+      <c r="C5">
+        <v>-6.7000000000000002E-5</v>
+      </c>
+      <c r="D5">
+        <v>-12.077</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1.47E-4</v>
+      </c>
+      <c r="B6">
+        <v>26.541</v>
+      </c>
+      <c r="C6">
+        <v>-4.6700000000000002E-4</v>
+      </c>
+      <c r="D6">
+        <v>-84.54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2.1100000000000001E-4</v>
+      </c>
+      <c r="B7">
+        <v>38.122999999999998</v>
+      </c>
+      <c r="C7">
+        <v>-4.8299999999999998E-4</v>
+      </c>
+      <c r="D7">
+        <v>-87.438000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2.6200000000000003E-4</v>
+      </c>
+      <c r="B8">
+        <v>47.387999999999998</v>
+      </c>
+      <c r="C8">
+        <v>-4.95E-4</v>
+      </c>
+      <c r="D8">
+        <v>-89.757000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>3.0299999999999999E-4</v>
+      </c>
+      <c r="B9">
+        <v>54.8</v>
+      </c>
+      <c r="C9">
+        <v>-4.9799999999999996E-4</v>
+      </c>
+      <c r="D9">
+        <v>-90.128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>3.3600000000000004E-4</v>
+      </c>
+      <c r="B10">
+        <v>60.73</v>
+      </c>
+      <c r="C10">
+        <v>-5.0600000000000005E-4</v>
+      </c>
+      <c r="D10">
+        <v>-82.048000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>3.4100000000000005E-4</v>
+      </c>
+      <c r="B11">
+        <v>60.231999999999999</v>
+      </c>
+      <c r="C11">
+        <v>-5.4700000000000007E-4</v>
+      </c>
+      <c r="D11">
+        <v>-82.683999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>3.6199999999999996E-4</v>
+      </c>
+      <c r="B12">
+        <v>58.488</v>
+      </c>
+      <c r="C12">
+        <v>-8.6700000000000004E-4</v>
+      </c>
+      <c r="D12">
+        <v>-102.792</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>4.6700000000000002E-4</v>
+      </c>
+      <c r="B13">
+        <v>66.293000000000006</v>
+      </c>
+      <c r="C13">
+        <v>-1.2669999999999999E-3</v>
+      </c>
+      <c r="D13">
+        <v>-124.22199999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>8.6700000000000004E-4</v>
+      </c>
+      <c r="B14">
+        <v>91.18</v>
+      </c>
+      <c r="C14">
+        <v>-1.6670000000000001E-3</v>
+      </c>
+      <c r="D14">
+        <v>-144.857</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1.2669999999999999E-3</v>
+      </c>
+      <c r="B15">
+        <v>113.87</v>
+      </c>
+      <c r="C15">
+        <v>-2.0670000000000003E-3</v>
+      </c>
+      <c r="D15">
+        <v>-165.40899999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1.6670000000000001E-3</v>
+      </c>
+      <c r="B16">
+        <v>136.40899999999999</v>
+      </c>
+      <c r="C16">
+        <v>-2.467E-3</v>
+      </c>
+      <c r="D16">
+        <v>-186.001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2.0670000000000003E-3</v>
+      </c>
+      <c r="B17">
+        <v>158.99700000000001</v>
+      </c>
+      <c r="C17">
+        <v>-2.8670000000000002E-3</v>
+      </c>
+      <c r="D17">
+        <v>-206.68299999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2.467E-3</v>
+      </c>
+      <c r="B18">
+        <v>181.67699999999999</v>
+      </c>
+      <c r="C18">
+        <v>-3.2669999999999999E-3</v>
+      </c>
+      <c r="D18">
+        <v>-227.452</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2.8670000000000002E-3</v>
+      </c>
+      <c r="B19">
+        <v>204.47900000000001</v>
+      </c>
+      <c r="C19">
+        <v>-3.6669999999999997E-3</v>
+      </c>
+      <c r="D19">
+        <v>-248.291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>3.2669999999999999E-3</v>
+      </c>
+      <c r="B20">
+        <v>227.34299999999999</v>
+      </c>
+      <c r="C20">
+        <v>-4.0670000000000003E-3</v>
+      </c>
+      <c r="D20">
+        <v>-269.18299999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>3.6669999999999997E-3</v>
+      </c>
+      <c r="B21">
+        <v>250.28200000000001</v>
+      </c>
+      <c r="C21">
+        <v>-4.4729999999999995E-3</v>
+      </c>
+      <c r="D21">
+        <v>-290.47000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>4.0670000000000003E-3</v>
+      </c>
+      <c r="B22">
+        <v>273.27699999999999</v>
+      </c>
+      <c r="C22">
+        <v>-4.921E-3</v>
+      </c>
+      <c r="D22">
+        <v>-313.916</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>4.4729999999999995E-3</v>
+      </c>
+      <c r="B23">
+        <v>296.70499999999998</v>
+      </c>
+      <c r="C23">
+        <v>-5.4130000000000003E-3</v>
+      </c>
+      <c r="D23">
+        <v>-339.726</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>4.921E-3</v>
+      </c>
+      <c r="B24">
+        <v>322.52199999999999</v>
+      </c>
+      <c r="C24">
+        <v>-5.9540000000000001E-3</v>
+      </c>
+      <c r="D24">
+        <v>-368.10500000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>5.4130000000000003E-3</v>
+      </c>
+      <c r="B25">
+        <v>350.96199999999999</v>
+      </c>
+      <c r="C25">
+        <v>-6.5490000000000001E-3</v>
+      </c>
+      <c r="D25">
+        <v>-399.29500000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>5.9540000000000001E-3</v>
+      </c>
+      <c r="B26">
+        <v>382.286</v>
+      </c>
+      <c r="C26">
+        <v>-7.2039999999999995E-3</v>
+      </c>
+      <c r="D26">
+        <v>-433.495</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>6.5490000000000001E-3</v>
+      </c>
+      <c r="B27">
+        <v>416.77199999999999</v>
+      </c>
+      <c r="C27">
+        <v>-7.9249999999999998E-3</v>
+      </c>
+      <c r="D27">
+        <v>-454.59399999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>7.2039999999999995E-3</v>
+      </c>
+      <c r="B28">
+        <v>427.30900000000003</v>
+      </c>
+      <c r="C28">
+        <v>-8.7170000000000008E-3</v>
+      </c>
+      <c r="D28">
+        <v>-456.87400000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>7.9249999999999998E-3</v>
+      </c>
+      <c r="B29">
+        <v>429.76499999999999</v>
+      </c>
+      <c r="C29">
+        <v>-9.5890000000000003E-3</v>
+      </c>
+      <c r="D29">
+        <v>-460.084</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>8.7170000000000008E-3</v>
+      </c>
+      <c r="B30">
+        <v>432.78300000000002</v>
+      </c>
+      <c r="C30">
+        <v>-1.0548E-2</v>
+      </c>
+      <c r="D30">
+        <v>-463.44099999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>9.5890000000000003E-3</v>
+      </c>
+      <c r="B31">
+        <v>436.38799999999998</v>
+      </c>
+      <c r="C31">
+        <v>-1.1603E-2</v>
+      </c>
+      <c r="D31">
+        <v>-466.87900000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>1.0548E-2</v>
+      </c>
+      <c r="B32">
+        <v>440.47300000000001</v>
+      </c>
+      <c r="C32">
+        <v>-1.2763E-2</v>
+      </c>
+      <c r="D32">
+        <v>-470.37900000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>1.1603E-2</v>
+      </c>
+      <c r="B33">
+        <v>445.21899999999999</v>
+      </c>
+      <c r="C33">
+        <v>-1.4038999999999999E-2</v>
+      </c>
+      <c r="D33">
+        <v>-473.96899999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>1.2763E-2</v>
+      </c>
+      <c r="B34">
+        <v>450.35399999999998</v>
+      </c>
+      <c r="C34">
+        <v>-1.5443E-2</v>
+      </c>
+      <c r="D34">
+        <v>-477.64499999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1.4038999999999999E-2</v>
+      </c>
+      <c r="B35">
+        <v>455.82799999999997</v>
+      </c>
+      <c r="C35">
+        <v>-1.6986999999999999E-2</v>
+      </c>
+      <c r="D35">
+        <v>-481.411</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1.5443E-2</v>
+      </c>
+      <c r="B36">
+        <v>461.61700000000002</v>
+      </c>
+      <c r="C36">
+        <v>-1.8686000000000001E-2</v>
+      </c>
+      <c r="D36">
+        <v>-485.20800000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1.6986999999999999E-2</v>
+      </c>
+      <c r="B37">
+        <v>466.92500000000001</v>
+      </c>
+      <c r="C37">
+        <v>-1.9059999999999997E-2</v>
+      </c>
+      <c r="D37">
+        <v>-486.12299999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1.8686000000000001E-2</v>
+      </c>
+      <c r="B38">
+        <v>470.767</v>
+      </c>
+      <c r="C38">
+        <v>-1.9359000000000001E-2</v>
+      </c>
+      <c r="D38">
+        <v>-486.73500000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>2.0555E-2</v>
+      </c>
+      <c r="B39">
+        <v>473.15100000000001</v>
+      </c>
+      <c r="C39">
+        <v>-1.9597999999999997E-2</v>
+      </c>
+      <c r="D39">
+        <v>-487.26900000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>2.2609999999999998E-2</v>
+      </c>
+      <c r="B40">
+        <v>474.89</v>
+      </c>
+      <c r="C40">
+        <v>-1.9789000000000001E-2</v>
+      </c>
+      <c r="D40">
+        <v>-487.65199999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>2.4870999999999997E-2</v>
+      </c>
+      <c r="B41">
+        <v>476.62599999999998</v>
+      </c>
+      <c r="C41">
+        <v>-1.9943000000000002E-2</v>
+      </c>
+      <c r="D41">
+        <v>-487.93700000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>2.7358E-2</v>
+      </c>
+      <c r="B42">
+        <v>478.35500000000002</v>
+      </c>
+      <c r="C42">
+        <v>-2.0065000000000003E-2</v>
+      </c>
+      <c r="D42">
+        <v>-488.21100000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>3.0094000000000003E-2</v>
+      </c>
+      <c r="B43">
+        <v>480.22300000000001</v>
+      </c>
+      <c r="C43">
+        <v>-2.0163E-2</v>
+      </c>
+      <c r="D43">
+        <v>-488.42399999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>3.3104000000000001E-2</v>
+      </c>
+      <c r="B44">
+        <v>481.83300000000003</v>
+      </c>
+      <c r="C44">
+        <v>-2.0240999999999999E-2</v>
+      </c>
+      <c r="D44">
+        <v>-488.59800000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>3.6414000000000002E-2</v>
+      </c>
+      <c r="B45">
+        <v>484.81799999999998</v>
+      </c>
+      <c r="C45">
+        <v>-2.0303999999999999E-2</v>
+      </c>
+      <c r="D45">
+        <v>-488.73399999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>3.6560000000000002E-2</v>
+      </c>
+      <c r="B46">
+        <v>485.02699999999999</v>
+      </c>
+      <c r="C46">
+        <v>-2.0354000000000001E-2</v>
+      </c>
+      <c r="D46">
+        <v>-488.84800000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>3.6676E-2</v>
+      </c>
+      <c r="B47">
+        <v>485.23200000000003</v>
+      </c>
+      <c r="C47">
+        <v>-2.0393999999999999E-2</v>
+      </c>
+      <c r="D47">
+        <v>-488.93799999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>3.6770000000000004E-2</v>
+      </c>
+      <c r="B48">
+        <v>485.35</v>
+      </c>
+      <c r="C48">
+        <v>-2.0555E-2</v>
+      </c>
+      <c r="D48">
+        <v>-489.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>3.6844000000000002E-2</v>
+      </c>
+      <c r="B49">
+        <v>485.46</v>
+      </c>
+      <c r="C49">
+        <v>-2.2609999999999998E-2</v>
+      </c>
+      <c r="D49">
+        <v>-493.267</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>3.6904000000000006E-2</v>
+      </c>
+      <c r="B50">
+        <v>485.56099999999998</v>
+      </c>
+      <c r="C50">
+        <v>-2.4870999999999997E-2</v>
+      </c>
+      <c r="D50">
+        <v>-497.161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>3.7142000000000001E-2</v>
+      </c>
+      <c r="B51">
+        <v>485.90600000000001</v>
+      </c>
+      <c r="C51">
+        <v>-2.7358E-2</v>
+      </c>
+      <c r="D51">
+        <v>-500.85300000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>4.0055999999999994E-2</v>
+      </c>
+      <c r="B52">
+        <v>490.375</v>
+      </c>
+      <c r="C52">
+        <v>-3.0094000000000003E-2</v>
+      </c>
+      <c r="D52">
+        <v>-504.10399999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>4.4061000000000003E-2</v>
+      </c>
+      <c r="B53">
+        <v>497.31299999999999</v>
+      </c>
+      <c r="C53">
+        <v>-3.3104000000000001E-2</v>
+      </c>
+      <c r="D53">
+        <v>-506.18599999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>4.8466999999999996E-2</v>
+      </c>
+      <c r="B54">
+        <v>503.85599999999999</v>
+      </c>
+      <c r="C54">
+        <v>-3.6414000000000002E-2</v>
+      </c>
+      <c r="D54">
+        <v>-504.726</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>5.3314E-2</v>
+      </c>
+      <c r="B55">
+        <v>509.60599999999999</v>
+      </c>
+      <c r="C55">
+        <v>-4.0055999999999994E-2</v>
+      </c>
+      <c r="D55">
+        <v>-503.452</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>5.8645000000000003E-2</v>
+      </c>
+      <c r="B56">
+        <v>513.92499999999995</v>
+      </c>
+      <c r="C56">
+        <v>-4.4061000000000003E-2</v>
+      </c>
+      <c r="D56">
+        <v>-504.24700000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>6.4510000000000012E-2</v>
+      </c>
+      <c r="B57">
+        <v>516.54600000000005</v>
+      </c>
+      <c r="C57">
+        <v>-4.8466999999999996E-2</v>
+      </c>
+      <c r="D57">
+        <v>-506.86099999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>7.0960999999999996E-2</v>
+      </c>
+      <c r="B58">
+        <v>517.83900000000006</v>
+      </c>
+      <c r="C58">
+        <v>-5.3314E-2</v>
+      </c>
+      <c r="D58">
+        <v>-510.327</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>7.8057000000000001E-2</v>
+      </c>
+      <c r="B59">
+        <v>518.57100000000003</v>
+      </c>
+      <c r="C59">
+        <v>-5.8645000000000003E-2</v>
+      </c>
+      <c r="D59">
+        <v>-510.959</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>8.5862999999999995E-2</v>
+      </c>
+      <c r="B60">
+        <v>519.43799999999999</v>
+      </c>
+      <c r="C60">
+        <v>-6.4510000000000012E-2</v>
+      </c>
+      <c r="D60">
+        <v>-510.15199999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>9.4448999999999991E-2</v>
+      </c>
+      <c r="B61">
+        <v>521.72199999999998</v>
+      </c>
+      <c r="C61">
+        <v>-7.0960999999999996E-2</v>
+      </c>
+      <c r="D61">
+        <v>-510.39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>0.103894</v>
+      </c>
+      <c r="B62">
+        <v>526.00699999999995</v>
+      </c>
+      <c r="C62">
+        <v>-7.8057000000000001E-2</v>
+      </c>
+      <c r="D62">
+        <v>-511.81200000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>0.114283</v>
+      </c>
+      <c r="B63">
+        <v>525.35799999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1BA886F-8DE5-439E-B8F7-8B32637C82FA}">
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>6.7000000000000002E-5</v>
+      </c>
+      <c r="B5">
+        <v>14.237</v>
+      </c>
+      <c r="C5">
+        <v>-6.7000000000000002E-5</v>
+      </c>
+      <c r="D5">
+        <v>-14.241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1.47E-4</v>
+      </c>
+      <c r="B6">
+        <v>31.321999999999999</v>
+      </c>
+      <c r="C6">
+        <v>-4.6700000000000002E-4</v>
+      </c>
+      <c r="D6">
+        <v>-99.682000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2.1100000000000001E-4</v>
+      </c>
+      <c r="B7">
+        <v>44.99</v>
+      </c>
+      <c r="C7">
+        <v>-5.4700000000000007E-4</v>
+      </c>
+      <c r="D7">
+        <v>-116.76900000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2.6200000000000003E-4</v>
+      </c>
+      <c r="B8">
+        <v>55.923999999999999</v>
+      </c>
+      <c r="C8">
+        <v>-6.11E-4</v>
+      </c>
+      <c r="D8">
+        <v>-130.43700000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2.7E-4</v>
+      </c>
+      <c r="B9">
+        <v>57.673999999999999</v>
+      </c>
+      <c r="C9">
+        <v>-6.6200000000000005E-4</v>
+      </c>
+      <c r="D9">
+        <v>-141.37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2.7700000000000001E-4</v>
+      </c>
+      <c r="B10">
+        <v>59.073999999999998</v>
+      </c>
+      <c r="C10">
+        <v>-6.7000000000000002E-4</v>
+      </c>
+      <c r="D10">
+        <v>-143.119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2.8199999999999997E-4</v>
+      </c>
+      <c r="B11">
+        <v>60.192999999999998</v>
+      </c>
+      <c r="C11">
+        <v>-6.7700000000000008E-4</v>
+      </c>
+      <c r="D11">
+        <v>-144.51900000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2.8599999999999996E-4</v>
+      </c>
+      <c r="B12">
+        <v>60.43</v>
+      </c>
+      <c r="C12">
+        <v>-6.820000000000001E-4</v>
+      </c>
+      <c r="D12">
+        <v>-122.751</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>3.0299999999999999E-4</v>
+      </c>
+      <c r="B13">
+        <v>54.625999999999998</v>
+      </c>
+      <c r="C13">
+        <v>-7.0299999999999996E-4</v>
+      </c>
+      <c r="D13">
+        <v>-123.76300000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>4.6700000000000002E-4</v>
+      </c>
+      <c r="B14">
+        <v>61.889000000000003</v>
+      </c>
+      <c r="C14">
+        <v>-8.6700000000000004E-4</v>
+      </c>
+      <c r="D14">
+        <v>-130.881</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>8.6700000000000004E-4</v>
+      </c>
+      <c r="B15">
+        <v>72.576999999999998</v>
+      </c>
+      <c r="C15">
+        <v>-1.2669999999999999E-3</v>
+      </c>
+      <c r="D15">
+        <v>-146.304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1.2669999999999999E-3</v>
+      </c>
+      <c r="B16">
+        <v>82.093999999999994</v>
+      </c>
+      <c r="C16">
+        <v>-1.6670000000000001E-3</v>
+      </c>
+      <c r="D16">
+        <v>-159.93700000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1.6670000000000001E-3</v>
+      </c>
+      <c r="B17">
+        <v>91.759</v>
+      </c>
+      <c r="C17">
+        <v>-2.0670000000000003E-3</v>
+      </c>
+      <c r="D17">
+        <v>-173.27600000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2.0670000000000003E-3</v>
+      </c>
+      <c r="B18">
+        <v>101.669</v>
+      </c>
+      <c r="C18">
+        <v>-2.467E-3</v>
+      </c>
+      <c r="D18">
+        <v>-186.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2.467E-3</v>
+      </c>
+      <c r="B19">
+        <v>111.777</v>
+      </c>
+      <c r="C19">
+        <v>-2.8670000000000002E-3</v>
+      </c>
+      <c r="D19">
+        <v>-200.233</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2.8670000000000002E-3</v>
+      </c>
+      <c r="B20">
+        <v>121.941</v>
+      </c>
+      <c r="C20">
+        <v>-3.2669999999999999E-3</v>
+      </c>
+      <c r="D20">
+        <v>-214.01</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>3.2669999999999999E-3</v>
+      </c>
+      <c r="B21">
+        <v>132.066</v>
+      </c>
+      <c r="C21">
+        <v>-3.6669999999999997E-3</v>
+      </c>
+      <c r="D21">
+        <v>-227.96899999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>3.6669999999999997E-3</v>
+      </c>
+      <c r="B22">
+        <v>142.23099999999999</v>
+      </c>
+      <c r="C22">
+        <v>-4.0670000000000003E-3</v>
+      </c>
+      <c r="D22">
+        <v>-242.077</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>4.0670000000000003E-3</v>
+      </c>
+      <c r="B23">
+        <v>152.43799999999999</v>
+      </c>
+      <c r="C23">
+        <v>-4.4729999999999995E-3</v>
+      </c>
+      <c r="D23">
+        <v>-256.55900000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>4.4729999999999995E-3</v>
+      </c>
+      <c r="B24">
+        <v>162.84100000000001</v>
+      </c>
+      <c r="C24">
+        <v>-4.921E-3</v>
+      </c>
+      <c r="D24">
+        <v>-272.61399999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>4.921E-3</v>
+      </c>
+      <c r="B25">
+        <v>173.065</v>
+      </c>
+      <c r="C25">
+        <v>-5.4130000000000003E-3</v>
+      </c>
+      <c r="D25">
+        <v>-290.26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>5.4130000000000003E-3</v>
+      </c>
+      <c r="B26">
+        <v>177.251</v>
+      </c>
+      <c r="C26">
+        <v>-5.9540000000000001E-3</v>
+      </c>
+      <c r="D26">
+        <v>-305.67099999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>5.9540000000000001E-3</v>
+      </c>
+      <c r="B27">
+        <v>178.572</v>
+      </c>
+      <c r="C27">
+        <v>-6.5490000000000001E-3</v>
+      </c>
+      <c r="D27">
+        <v>-307.536</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>6.5490000000000001E-3</v>
+      </c>
+      <c r="B28">
+        <v>180.59</v>
+      </c>
+      <c r="C28">
+        <v>-7.2039999999999995E-3</v>
+      </c>
+      <c r="D28">
+        <v>-309.495</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>7.2039999999999995E-3</v>
+      </c>
+      <c r="B29">
+        <v>182.85300000000001</v>
+      </c>
+      <c r="C29">
+        <v>-7.9249999999999998E-3</v>
+      </c>
+      <c r="D29">
+        <v>-312.04300000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>7.9249999999999998E-3</v>
+      </c>
+      <c r="B30">
+        <v>185.274</v>
+      </c>
+      <c r="C30">
+        <v>-8.7170000000000008E-3</v>
+      </c>
+      <c r="D30">
+        <v>-315.17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>8.7170000000000008E-3</v>
+      </c>
+      <c r="B31">
+        <v>187.994</v>
+      </c>
+      <c r="C31">
+        <v>-9.5890000000000003E-3</v>
+      </c>
+      <c r="D31">
+        <v>-318.42200000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>9.5890000000000003E-3</v>
+      </c>
+      <c r="B32">
+        <v>191.00299999999999</v>
+      </c>
+      <c r="C32">
+        <v>-1.0548E-2</v>
+      </c>
+      <c r="D32">
+        <v>-321.81299999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>1.0548E-2</v>
+      </c>
+      <c r="B33">
+        <v>194.27500000000001</v>
+      </c>
+      <c r="C33">
+        <v>-1.1603E-2</v>
+      </c>
+      <c r="D33">
+        <v>-325.358</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>1.1603E-2</v>
+      </c>
+      <c r="B34">
+        <v>197.78299999999999</v>
+      </c>
+      <c r="C34">
+        <v>-1.2763E-2</v>
+      </c>
+      <c r="D34">
+        <v>-329.01799999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1.2763E-2</v>
+      </c>
+      <c r="B35">
+        <v>200.988</v>
+      </c>
+      <c r="C35">
+        <v>-1.4038999999999999E-2</v>
+      </c>
+      <c r="D35">
+        <v>-332.91899999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1.4038999999999999E-2</v>
+      </c>
+      <c r="B36">
+        <v>201.79900000000001</v>
+      </c>
+      <c r="C36">
+        <v>-1.5443E-2</v>
+      </c>
+      <c r="D36">
+        <v>-337.12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1.5443E-2</v>
+      </c>
+      <c r="B37">
+        <v>202.40299999999999</v>
+      </c>
+      <c r="C37">
+        <v>-1.6986999999999999E-2</v>
+      </c>
+      <c r="D37">
+        <v>-341.36200000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1.6986999999999999E-2</v>
+      </c>
+      <c r="B38">
+        <v>202.92500000000001</v>
+      </c>
+      <c r="C38">
+        <v>-1.8686000000000001E-2</v>
+      </c>
+      <c r="D38">
+        <v>-345.87700000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1.8686000000000001E-2</v>
+      </c>
+      <c r="B39">
+        <v>203.42699999999999</v>
+      </c>
+      <c r="C39">
+        <v>-2.0555E-2</v>
+      </c>
+      <c r="D39">
+        <v>-350.63900000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>2.0555E-2</v>
+      </c>
+      <c r="B40">
+        <v>203.78800000000001</v>
+      </c>
+      <c r="C40">
+        <v>-2.2609999999999998E-2</v>
+      </c>
+      <c r="D40">
+        <v>-355.55200000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>2.2609999999999998E-2</v>
+      </c>
+      <c r="B41">
+        <v>204.07599999999999</v>
+      </c>
+      <c r="C41">
+        <v>-2.4870999999999997E-2</v>
+      </c>
+      <c r="D41">
+        <v>-360.70100000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>2.4870999999999997E-2</v>
+      </c>
+      <c r="B42">
+        <v>204.24799999999999</v>
+      </c>
+      <c r="C42">
+        <v>-2.4971E-2</v>
+      </c>
+      <c r="D42">
+        <v>-360.91500000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>2.7358E-2</v>
+      </c>
+      <c r="B43">
+        <v>204.434</v>
+      </c>
+      <c r="C43">
+        <v>-2.5049999999999999E-2</v>
+      </c>
+      <c r="D43">
+        <v>-361.09100000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>3.0094000000000003E-2</v>
+      </c>
+      <c r="B44">
+        <v>204.761</v>
+      </c>
+      <c r="C44">
+        <v>-2.5114000000000001E-2</v>
+      </c>
+      <c r="D44">
+        <v>-361.233</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>3.3104000000000001E-2</v>
+      </c>
+      <c r="B45">
+        <v>205.37200000000001</v>
+      </c>
+      <c r="C45">
+        <v>-2.5165E-2</v>
+      </c>
+      <c r="D45">
+        <v>-361.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>3.6414000000000002E-2</v>
+      </c>
+      <c r="B46">
+        <v>208.07</v>
+      </c>
+      <c r="C46">
+        <v>-2.5205999999999999E-2</v>
+      </c>
+      <c r="D46">
+        <v>-361.42200000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>4.0055999999999994E-2</v>
+      </c>
+      <c r="B47">
+        <v>211.08199999999999</v>
+      </c>
+      <c r="C47">
+        <v>-2.5238E-2</v>
+      </c>
+      <c r="D47">
+        <v>-361.58300000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>4.4061000000000003E-2</v>
+      </c>
+      <c r="B48">
+        <v>214.428</v>
+      </c>
+      <c r="C48">
+        <v>-2.5263999999999998E-2</v>
+      </c>
+      <c r="D48">
+        <v>-361.64400000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>4.8466999999999996E-2</v>
+      </c>
+      <c r="B49">
+        <v>218.08199999999999</v>
+      </c>
+      <c r="C49">
+        <v>-2.5368999999999999E-2</v>
+      </c>
+      <c r="D49">
+        <v>-361.78500000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>5.3314E-2</v>
+      </c>
+      <c r="B50">
+        <v>222.15799999999999</v>
+      </c>
+      <c r="C50">
+        <v>-2.7358E-2</v>
+      </c>
+      <c r="D50">
+        <v>-366.00700000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>5.8645000000000003E-2</v>
+      </c>
+      <c r="B51">
+        <v>226.501</v>
+      </c>
+      <c r="C51">
+        <v>-3.0094000000000003E-2</v>
+      </c>
+      <c r="D51">
+        <v>-369.31799999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>6.4510000000000012E-2</v>
+      </c>
+      <c r="B52">
+        <v>230.75899999999999</v>
+      </c>
+      <c r="C52">
+        <v>-3.3104000000000001E-2</v>
+      </c>
+      <c r="D52">
+        <v>-367.791</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>6.5799999999999997E-2</v>
+      </c>
+      <c r="B53">
+        <v>231.58099999999999</v>
+      </c>
+      <c r="C53">
+        <v>-3.6414000000000002E-2</v>
+      </c>
+      <c r="D53">
+        <v>-366.04</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>6.7219000000000001E-2</v>
+      </c>
+      <c r="B54">
+        <v>232.39099999999999</v>
+      </c>
+      <c r="C54">
+        <v>-4.0055999999999994E-2</v>
+      </c>
+      <c r="D54">
+        <v>-366.75700000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>6.7511000000000002E-2</v>
+      </c>
+      <c r="B55">
+        <v>232.54400000000001</v>
+      </c>
+      <c r="C55">
+        <v>-4.4061000000000003E-2</v>
+      </c>
+      <c r="D55">
+        <v>-367.834</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>6.7808999999999994E-2</v>
+      </c>
+      <c r="B56">
+        <v>232.70099999999999</v>
+      </c>
+      <c r="C56">
+        <v>-4.8466999999999996E-2</v>
+      </c>
+      <c r="D56">
+        <v>-368.6</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C57">
-        <v>-3.0812000000000003E-2</v>
+        <v>-5.3314E-2</v>
       </c>
       <c r="D57">
-        <v>-379.649</v>
+        <v>-368.92599999999999</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C58">
-        <v>-3.3893E-2</v>
+        <v>-5.8645000000000003E-2</v>
       </c>
       <c r="D58">
-        <v>-381.52199999999999</v>
+        <v>-369.34800000000001</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C59">
-        <v>-3.7283000000000004E-2</v>
+        <v>-6.4510000000000012E-2</v>
       </c>
       <c r="D59">
-        <v>-383.49200000000002</v>
+        <v>-370.13799999999998</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C60">
-        <v>-4.1011000000000006E-2</v>
+        <v>-7.0960999999999996E-2</v>
       </c>
       <c r="D60">
-        <v>-385.464</v>
+        <v>-369.59399999999999</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C61">
-        <v>-4.5111999999999999E-2</v>
+        <v>-7.8057000000000001E-2</v>
       </c>
       <c r="D61">
-        <v>-387.47199999999998</v>
+        <v>-350.59699999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB666397-9C42-416B-9385-0E742D1FF9CD}">
+  <dimension ref="A1:D73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>6.7000000000000002E-5</v>
+      </c>
+      <c r="B5">
+        <v>11.061</v>
+      </c>
+      <c r="C5">
+        <v>-6.7000000000000002E-5</v>
+      </c>
+      <c r="D5">
+        <v>-11.065</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1.47E-4</v>
+      </c>
+      <c r="B6">
+        <v>24.335000000000001</v>
+      </c>
+      <c r="C6">
+        <v>-4.6700000000000002E-4</v>
+      </c>
+      <c r="D6">
+        <v>-77.456999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2.1100000000000001E-4</v>
+      </c>
+      <c r="B7">
+        <v>34.953000000000003</v>
+      </c>
+      <c r="C7">
+        <v>-4.8299999999999998E-4</v>
+      </c>
+      <c r="D7">
+        <v>-80.111999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2.6200000000000003E-4</v>
+      </c>
+      <c r="B8">
+        <v>43.448999999999998</v>
+      </c>
+      <c r="C8">
+        <v>-4.95E-4</v>
+      </c>
+      <c r="D8">
+        <v>-82.236999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>3.0299999999999999E-4</v>
+      </c>
+      <c r="B9">
+        <v>50.244999999999997</v>
+      </c>
+      <c r="C9">
+        <v>-5.0600000000000005E-4</v>
+      </c>
+      <c r="D9">
+        <v>-83.936000000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>3.0899999999999998E-4</v>
+      </c>
+      <c r="B10">
+        <v>51.332000000000001</v>
+      </c>
+      <c r="C10">
+        <v>-5.1400000000000003E-4</v>
+      </c>
+      <c r="D10">
+        <v>-85.296000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>3.1500000000000001E-4</v>
+      </c>
+      <c r="B11">
+        <v>52.201999999999998</v>
+      </c>
+      <c r="C11">
+        <v>-5.2000000000000006E-4</v>
+      </c>
+      <c r="D11">
+        <v>-73.114000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>3.19E-4</v>
+      </c>
+      <c r="B12">
+        <v>52.898000000000003</v>
+      </c>
+      <c r="C12">
+        <v>-5.4700000000000007E-4</v>
+      </c>
+      <c r="D12">
+        <v>-74.317999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>3.2200000000000002E-4</v>
+      </c>
+      <c r="B13">
+        <v>53.454000000000001</v>
+      </c>
+      <c r="C13">
+        <v>-8.6700000000000004E-4</v>
+      </c>
+      <c r="D13">
+        <v>-88.424999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>3.2499999999999999E-4</v>
+      </c>
+      <c r="B14">
+        <v>53.9</v>
+      </c>
+      <c r="C14">
+        <v>-1.2669999999999999E-3</v>
+      </c>
+      <c r="D14">
+        <v>-102.008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>3.2700000000000003E-4</v>
+      </c>
+      <c r="B15">
+        <v>54.256</v>
+      </c>
+      <c r="C15">
+        <v>-1.6670000000000001E-3</v>
+      </c>
+      <c r="D15">
+        <v>-114.556</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>3.2900000000000003E-4</v>
+      </c>
+      <c r="B16">
+        <v>54.540999999999997</v>
+      </c>
+      <c r="C16">
+        <v>-2.0670000000000003E-3</v>
+      </c>
+      <c r="D16">
+        <v>-126.949</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>3.3E-4</v>
+      </c>
+      <c r="B17">
+        <v>54.768999999999998</v>
+      </c>
+      <c r="C17">
+        <v>-2.467E-3</v>
+      </c>
+      <c r="D17">
+        <v>-139.36500000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>3.3600000000000004E-4</v>
+      </c>
+      <c r="B18">
+        <v>52.439</v>
+      </c>
+      <c r="C18">
+        <v>-2.8670000000000002E-3</v>
+      </c>
+      <c r="D18">
+        <v>-151.893</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>4.6700000000000002E-4</v>
+      </c>
+      <c r="B19">
+        <v>55.128</v>
+      </c>
+      <c r="C19">
+        <v>-3.2669999999999999E-3</v>
+      </c>
+      <c r="D19">
+        <v>-164.511</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>8.6700000000000004E-4</v>
+      </c>
+      <c r="B20">
+        <v>66.394999999999996</v>
+      </c>
+      <c r="C20">
+        <v>-3.6669999999999997E-3</v>
+      </c>
+      <c r="D20">
+        <v>-177.24799999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1.2669999999999999E-3</v>
+      </c>
+      <c r="B21">
+        <v>75.426000000000002</v>
+      </c>
+      <c r="C21">
+        <v>-4.0670000000000003E-3</v>
+      </c>
+      <c r="D21">
+        <v>-190.083</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1.6670000000000001E-3</v>
+      </c>
+      <c r="B22">
+        <v>84.266999999999996</v>
+      </c>
+      <c r="C22">
+        <v>-4.4729999999999995E-3</v>
+      </c>
+      <c r="D22">
+        <v>-203.196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2.0670000000000003E-3</v>
+      </c>
+      <c r="B23">
+        <v>93.221000000000004</v>
+      </c>
+      <c r="C23">
+        <v>-4.921E-3</v>
+      </c>
+      <c r="D23">
+        <v>-217.69900000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2.467E-3</v>
+      </c>
+      <c r="B24">
+        <v>102.31399999999999</v>
+      </c>
+      <c r="C24">
+        <v>-5.4130000000000003E-3</v>
+      </c>
+      <c r="D24">
+        <v>-233.72300000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2.8670000000000002E-3</v>
+      </c>
+      <c r="B25">
+        <v>111.547</v>
+      </c>
+      <c r="C25">
+        <v>-5.9540000000000001E-3</v>
+      </c>
+      <c r="D25">
+        <v>-251.30699999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3.2669999999999999E-3</v>
+      </c>
+      <c r="B26">
+        <v>120.899</v>
+      </c>
+      <c r="C26">
+        <v>-6.5490000000000001E-3</v>
+      </c>
+      <c r="D26">
+        <v>-259.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3.6669999999999997E-3</v>
+      </c>
+      <c r="B27">
+        <v>130.352</v>
+      </c>
+      <c r="C27">
+        <v>-7.2039999999999995E-3</v>
+      </c>
+      <c r="D27">
+        <v>-260.46899999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>4.0670000000000003E-3</v>
+      </c>
+      <c r="B28">
+        <v>139.88999999999999</v>
+      </c>
+      <c r="C28">
+        <v>-7.9249999999999998E-3</v>
+      </c>
+      <c r="D28">
+        <v>-262.46300000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>4.4729999999999995E-3</v>
+      </c>
+      <c r="B29">
+        <v>149.65199999999999</v>
+      </c>
+      <c r="C29">
+        <v>-8.7170000000000008E-3</v>
+      </c>
+      <c r="D29">
+        <v>-264.80399999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4.921E-3</v>
+      </c>
+      <c r="B30">
+        <v>160.26400000000001</v>
+      </c>
+      <c r="C30">
+        <v>-9.5890000000000003E-3</v>
+      </c>
+      <c r="D30">
+        <v>-267.24200000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>5.4130000000000003E-3</v>
+      </c>
+      <c r="B31">
+        <v>168.328</v>
+      </c>
+      <c r="C31">
+        <v>-1.0548E-2</v>
+      </c>
+      <c r="D31">
+        <v>-269.786</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>5.9540000000000001E-3</v>
+      </c>
+      <c r="B32">
+        <v>168.89099999999999</v>
+      </c>
+      <c r="C32">
+        <v>-1.1603E-2</v>
+      </c>
+      <c r="D32">
+        <v>-272.45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>6.5490000000000001E-3</v>
+      </c>
+      <c r="B33">
+        <v>169.93799999999999</v>
+      </c>
+      <c r="C33">
+        <v>-1.2763E-2</v>
+      </c>
+      <c r="D33">
+        <v>-275.24599999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>7.2039999999999995E-3</v>
+      </c>
+      <c r="B34">
+        <v>171.50800000000001</v>
+      </c>
+      <c r="C34">
+        <v>-1.4038999999999999E-2</v>
+      </c>
+      <c r="D34">
+        <v>-278.18700000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>7.9249999999999998E-3</v>
+      </c>
+      <c r="B35">
+        <v>173.24700000000001</v>
+      </c>
+      <c r="C35">
+        <v>-1.5443E-2</v>
+      </c>
+      <c r="D35">
+        <v>-281.26799999999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>8.7170000000000008E-3</v>
+      </c>
+      <c r="B36">
+        <v>175.20500000000001</v>
+      </c>
+      <c r="C36">
+        <v>-1.6986999999999999E-2</v>
+      </c>
+      <c r="D36">
+        <v>-284.54199999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>9.5890000000000003E-3</v>
+      </c>
+      <c r="B37">
+        <v>177.35499999999999</v>
+      </c>
+      <c r="C37">
+        <v>-1.8686000000000001E-2</v>
+      </c>
+      <c r="D37">
+        <v>-288.04399999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1.0548E-2</v>
+      </c>
+      <c r="B38">
+        <v>179.58500000000001</v>
+      </c>
+      <c r="C38">
+        <v>-2.0555E-2</v>
+      </c>
+      <c r="D38">
+        <v>-291.68400000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1.1603E-2</v>
+      </c>
+      <c r="B39">
+        <v>181.97200000000001</v>
+      </c>
+      <c r="C39">
+        <v>-2.2609999999999998E-2</v>
+      </c>
+      <c r="D39">
+        <v>-295.505</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1.2763E-2</v>
+      </c>
+      <c r="B40">
+        <v>184.511</v>
+      </c>
+      <c r="C40">
+        <v>-2.4870999999999997E-2</v>
+      </c>
+      <c r="D40">
+        <v>-299.33800000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1.4038999999999999E-2</v>
+      </c>
+      <c r="B41">
+        <v>187.21899999999999</v>
+      </c>
+      <c r="C41">
+        <v>-2.7358E-2</v>
+      </c>
+      <c r="D41">
+        <v>-301.22500000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>1.5443E-2</v>
+      </c>
+      <c r="B42">
+        <v>190.06899999999999</v>
+      </c>
+      <c r="C42">
+        <v>-2.7906E-2</v>
+      </c>
+      <c r="D42">
+        <v>-301.12799999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1.6986999999999999E-2</v>
+      </c>
+      <c r="B43">
+        <v>192.18199999999999</v>
+      </c>
+      <c r="C43">
+        <v>-2.8343E-2</v>
+      </c>
+      <c r="D43">
+        <v>-301.01600000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1.8686000000000001E-2</v>
+      </c>
+      <c r="B44">
+        <v>192.77799999999999</v>
+      </c>
+      <c r="C44">
+        <v>-2.8694000000000001E-2</v>
+      </c>
+      <c r="D44">
+        <v>-300.976</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>2.0555E-2</v>
+      </c>
+      <c r="B45">
+        <v>193.14099999999999</v>
+      </c>
+      <c r="C45">
+        <v>-2.8974E-2</v>
+      </c>
+      <c r="D45">
+        <v>-300.92200000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>2.2609999999999998E-2</v>
+      </c>
+      <c r="B46">
+        <v>193.40799999999999</v>
+      </c>
+      <c r="C46">
+        <v>-2.9198000000000002E-2</v>
+      </c>
+      <c r="D46">
+        <v>-300.87799999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>2.4870999999999997E-2</v>
+      </c>
+      <c r="B47">
+        <v>193.65100000000001</v>
+      </c>
+      <c r="C47">
+        <v>-2.9377E-2</v>
+      </c>
+      <c r="D47">
+        <v>-300.839</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>2.7358E-2</v>
+      </c>
+      <c r="B48">
+        <v>193.86500000000001</v>
+      </c>
+      <c r="C48">
+        <v>-2.9521000000000002E-2</v>
+      </c>
+      <c r="D48">
+        <v>-300.81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>3.0094000000000003E-2</v>
+      </c>
+      <c r="B49">
+        <v>194.041</v>
+      </c>
+      <c r="C49">
+        <v>-2.9635000000000002E-2</v>
+      </c>
+      <c r="D49">
+        <v>-300.786</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>3.3104000000000001E-2</v>
+      </c>
+      <c r="B50">
+        <v>194.22399999999999</v>
+      </c>
+      <c r="C50">
+        <v>-3.0094000000000003E-2</v>
+      </c>
+      <c r="D50">
+        <v>-300.68299999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>3.6414000000000002E-2</v>
+      </c>
+      <c r="B51">
+        <v>196.26</v>
+      </c>
+      <c r="C51">
+        <v>-3.3104000000000001E-2</v>
+      </c>
+      <c r="D51">
+        <v>-300.01100000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>4.0055999999999994E-2</v>
+      </c>
+      <c r="B52">
+        <v>198.76</v>
+      </c>
+      <c r="C52">
+        <v>-3.6414000000000002E-2</v>
+      </c>
+      <c r="D52">
+        <v>-299.62200000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>4.4061000000000003E-2</v>
+      </c>
+      <c r="B53">
+        <v>201.523</v>
+      </c>
+      <c r="C53">
+        <v>-4.0055999999999994E-2</v>
+      </c>
+      <c r="D53">
+        <v>-301.64499999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>4.8466999999999996E-2</v>
+      </c>
+      <c r="B54">
+        <v>204.529</v>
+      </c>
+      <c r="C54">
+        <v>-4.4061000000000003E-2</v>
+      </c>
+      <c r="D54">
+        <v>-303.80799999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>5.3314E-2</v>
+      </c>
+      <c r="B55">
+        <v>207.79400000000001</v>
+      </c>
+      <c r="C55">
+        <v>-4.8466999999999996E-2</v>
+      </c>
+      <c r="D55">
+        <v>-305.73399999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>5.8645000000000003E-2</v>
+      </c>
+      <c r="B56">
+        <v>211.29300000000001</v>
+      </c>
+      <c r="C56">
+        <v>-5.3314E-2</v>
+      </c>
+      <c r="D56">
+        <v>-307.39100000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>5.9817999999999996E-2</v>
+      </c>
+      <c r="B57">
+        <v>212.041</v>
+      </c>
+      <c r="C57">
+        <v>-5.8645000000000003E-2</v>
+      </c>
+      <c r="D57">
+        <v>-308.75299999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>6.0756999999999999E-2</v>
+      </c>
+      <c r="B58">
+        <v>212.63800000000001</v>
+      </c>
+      <c r="C58">
+        <v>-6.4510000000000012E-2</v>
+      </c>
+      <c r="D58">
+        <v>-309.86799999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>6.1506999999999999E-2</v>
+      </c>
+      <c r="B59">
+        <v>213.102</v>
+      </c>
+      <c r="C59">
+        <v>-7.0960999999999996E-2</v>
+      </c>
+      <c r="D59">
+        <v>-311.16399999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>6.2107999999999997E-2</v>
+      </c>
+      <c r="B60">
+        <v>213.48500000000001</v>
+      </c>
+      <c r="C60">
+        <v>-7.8057000000000001E-2</v>
+      </c>
+      <c r="D60">
+        <v>-312.82100000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>6.2204000000000002E-2</v>
+      </c>
+      <c r="B61">
+        <v>213.52199999999999</v>
+      </c>
+      <c r="C61">
+        <v>-8.5862999999999995E-2</v>
+      </c>
+      <c r="D61">
+        <v>-315.36900000000003</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>6.2280999999999996E-2</v>
+      </c>
+      <c r="B62">
+        <v>213.584</v>
+      </c>
       <c r="C62">
-        <v>-4.9623E-2</v>
+        <v>-9.4448999999999991E-2</v>
       </c>
       <c r="D62">
-        <v>-389.476</v>
+        <v>-316.22800000000001</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>6.2588000000000005E-2</v>
+      </c>
+      <c r="B63">
+        <v>213.78</v>
+      </c>
       <c r="C63">
-        <v>-5.4585000000000002E-2</v>
+        <v>-0.103894</v>
       </c>
       <c r="D63">
-        <v>-391.43</v>
+        <v>-300.69900000000001</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C64">
-        <v>-6.0044E-2</v>
-      </c>
-      <c r="D64">
-        <v>-393.26499999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C65">
-        <v>-6.6047999999999996E-2</v>
-      </c>
-      <c r="D65">
-        <v>-395.084</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C66">
-        <v>-7.2653000000000009E-2</v>
-      </c>
-      <c r="D66">
-        <v>-396.858</v>
+      <c r="A64">
+        <v>6.4510000000000012E-2</v>
+      </c>
+      <c r="B64">
+        <v>214.96600000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>7.0960999999999996E-2</v>
+      </c>
+      <c r="B65">
+        <v>218.66300000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>7.8057000000000001E-2</v>
+      </c>
+      <c r="B66">
+        <v>222.167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>8.5862999999999995E-2</v>
+      </c>
+      <c r="B67">
+        <v>225.191</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>9.4448999999999991E-2</v>
+      </c>
+      <c r="B68">
+        <v>227.28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>9.6337999999999993E-2</v>
+      </c>
+      <c r="B69">
+        <v>227.53299999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>9.6754000000000007E-2</v>
+      </c>
+      <c r="B70">
+        <v>227.53299999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>9.7180000000000002E-2</v>
+      </c>
+      <c r="B71">
+        <v>227.59899999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>9.7610000000000002E-2</v>
+      </c>
+      <c r="B72">
+        <v>227.631</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>9.8042000000000004E-2</v>
+      </c>
+      <c r="B73">
+        <v>227.654</v>
       </c>
     </row>
   </sheetData>
